--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -4525,10 +4525,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133623428</v>
+        <v>133623404</v>
       </c>
       <c r="B41" t="n">
-        <v>91918</v>
+        <v>79365</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4536,21 +4536,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>620196</v>
+        <v>620098</v>
       </c>
       <c r="R41" t="n">
-        <v>6898931</v>
+        <v>6898939</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4622,10 +4622,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133623424</v>
+        <v>133623428</v>
       </c>
       <c r="B42" t="n">
-        <v>79952</v>
+        <v>91918</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4633,21 +4633,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4657,10 +4657,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620238</v>
+        <v>620196</v>
       </c>
       <c r="R42" t="n">
-        <v>6898939</v>
+        <v>6898931</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4719,10 +4719,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133623404</v>
+        <v>133623424</v>
       </c>
       <c r="B43" t="n">
-        <v>79365</v>
+        <v>79952</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4730,21 +4730,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4754,7 +4754,7 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620098</v>
+        <v>620238</v>
       </c>
       <c r="R43" t="n">
         <v>6898939</v>

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133623415</v>
+        <v>133623413</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>79333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620235</v>
+        <v>620178</v>
       </c>
       <c r="R2" t="n">
-        <v>6898961</v>
+        <v>6898953</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133623413</v>
+        <v>133623447</v>
       </c>
       <c r="B3" t="n">
         <v>79333</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620178</v>
+        <v>620318</v>
       </c>
       <c r="R3" t="n">
-        <v>6898953</v>
+        <v>6898875</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133623447</v>
+        <v>133623415</v>
       </c>
       <c r="B4" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620318</v>
+        <v>620235</v>
       </c>
       <c r="R4" t="n">
-        <v>6898875</v>
+        <v>6898961</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133623455</v>
+        <v>133623410</v>
       </c>
       <c r="B8" t="n">
-        <v>91881</v>
+        <v>79365</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620268</v>
+        <v>620159</v>
       </c>
       <c r="R8" t="n">
-        <v>6898926</v>
+        <v>6898960</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133623410</v>
+        <v>133623403</v>
       </c>
       <c r="B9" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620159</v>
+        <v>620099</v>
       </c>
       <c r="R9" t="n">
-        <v>6898960</v>
+        <v>6898937</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133623403</v>
+        <v>133623455</v>
       </c>
       <c r="B10" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620099</v>
+        <v>620268</v>
       </c>
       <c r="R10" t="n">
-        <v>6898937</v>
+        <v>6898926</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133623431</v>
+        <v>133623411</v>
       </c>
       <c r="B17" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620266</v>
+        <v>620166</v>
       </c>
       <c r="R17" t="n">
-        <v>6898928</v>
+        <v>6898962</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2242,54 +2242,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133623442</v>
+        <v>133623431</v>
       </c>
       <c r="B18" t="n">
-        <v>4775</v>
+        <v>79333</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620347</v>
+        <v>620266</v>
       </c>
       <c r="R18" t="n">
-        <v>6898852</v>
+        <v>6898928</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2330,7 +2321,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2349,45 +2339,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133623411</v>
+        <v>133623442</v>
       </c>
       <c r="B19" t="n">
-        <v>79365</v>
+        <v>4775</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>100299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620166</v>
+        <v>620347</v>
       </c>
       <c r="R19" t="n">
-        <v>6898962</v>
+        <v>6898852</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2428,6 +2427,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2844,32 +2844,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133623452</v>
+        <v>133623422</v>
       </c>
       <c r="B24" t="n">
-        <v>91881</v>
+        <v>80438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620384</v>
+        <v>620275</v>
       </c>
       <c r="R24" t="n">
-        <v>6898898</v>
+        <v>6898953</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133623422</v>
+        <v>133623444</v>
       </c>
       <c r="B25" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2952,21 +2952,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620275</v>
+        <v>620341</v>
       </c>
       <c r="R25" t="n">
-        <v>6898953</v>
+        <v>6898817</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3038,32 +3038,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133623444</v>
+        <v>133623452</v>
       </c>
       <c r="B26" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620341</v>
+        <v>620384</v>
       </c>
       <c r="R26" t="n">
-        <v>6898817</v>
+        <v>6898898</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3135,53 +3135,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133623446</v>
+        <v>133623426</v>
       </c>
       <c r="B27" t="n">
-        <v>57958</v>
+        <v>91881</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620339</v>
+        <v>620174</v>
       </c>
       <c r="R27" t="n">
-        <v>6898847</v>
+        <v>6898936</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3237,48 +3232,56 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133623426</v>
+        <v>133623402</v>
       </c>
       <c r="B28" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620174</v>
+        <v>620109</v>
       </c>
       <c r="R28" t="n">
-        <v>6898936</v>
+        <v>6898948</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3334,10 +3337,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133623458</v>
+        <v>133623446</v>
       </c>
       <c r="B29" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3345,37 +3348,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620239</v>
+        <v>620339</v>
       </c>
       <c r="R29" t="n">
-        <v>6898916</v>
+        <v>6898847</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3431,10 +3439,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133623463</v>
+        <v>133623458</v>
       </c>
       <c r="B30" t="n">
-        <v>92649</v>
+        <v>91918</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3442,37 +3450,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>757</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620142</v>
+        <v>620239</v>
       </c>
       <c r="R30" t="n">
-        <v>6898946</v>
+        <v>6898916</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3507,18 +3512,12 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3537,10 +3536,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133623402</v>
+        <v>133623463</v>
       </c>
       <c r="B31" t="n">
-        <v>57958</v>
+        <v>92649</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3548,31 +3547,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>757</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3580,13 +3574,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620109</v>
+        <v>620142</v>
       </c>
       <c r="R31" t="n">
-        <v>6898948</v>
+        <v>6898946</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3618,12 +3612,18 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3938,32 +3938,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133623464</v>
+        <v>133623459</v>
       </c>
       <c r="B35" t="n">
-        <v>91881</v>
+        <v>81318</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>1049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3973,10 +3973,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>620127</v>
+        <v>620266</v>
       </c>
       <c r="R35" t="n">
-        <v>6898927</v>
+        <v>6898988</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4035,32 +4035,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133623459</v>
+        <v>133623464</v>
       </c>
       <c r="B36" t="n">
-        <v>81318</v>
+        <v>91881</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1049</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620266</v>
+        <v>620127</v>
       </c>
       <c r="R36" t="n">
-        <v>6898988</v>
+        <v>6898927</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4132,32 +4132,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133623432</v>
+        <v>133623421</v>
       </c>
       <c r="B37" t="n">
-        <v>91881</v>
+        <v>79365</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620266</v>
+        <v>620249</v>
       </c>
       <c r="R37" t="n">
-        <v>6898927</v>
+        <v>6898992</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4229,32 +4229,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133623421</v>
+        <v>133623432</v>
       </c>
       <c r="B38" t="n">
-        <v>79365</v>
+        <v>91881</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4264,10 +4264,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>620249</v>
+        <v>620266</v>
       </c>
       <c r="R38" t="n">
-        <v>6898992</v>
+        <v>6898927</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -869,48 +869,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133623415</v>
+        <v>133623460</v>
       </c>
       <c r="B4" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620235</v>
+        <v>620244</v>
       </c>
       <c r="R4" t="n">
-        <v>6898961</v>
+        <v>6898934</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -940,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,53 +976,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133623460</v>
+        <v>133623415</v>
       </c>
       <c r="B5" t="n">
-        <v>57958</v>
+        <v>91881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620244</v>
+        <v>620235</v>
       </c>
       <c r="R5" t="n">
-        <v>6898934</v>
+        <v>6898961</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1042,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133623435</v>
+        <v>133623403</v>
       </c>
       <c r="B6" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620315</v>
+        <v>620099</v>
       </c>
       <c r="R6" t="n">
-        <v>6899013</v>
+        <v>6898937</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133623430</v>
+        <v>133623455</v>
       </c>
       <c r="B7" t="n">
-        <v>79365</v>
+        <v>91881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620267</v>
+        <v>620268</v>
       </c>
       <c r="R7" t="n">
-        <v>6898931</v>
+        <v>6898926</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1267,7 +1267,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133623410</v>
+        <v>133623435</v>
       </c>
       <c r="B8" t="n">
         <v>79365</v>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620159</v>
+        <v>620315</v>
       </c>
       <c r="R8" t="n">
-        <v>6898960</v>
+        <v>6899013</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133623403</v>
+        <v>133623430</v>
       </c>
       <c r="B9" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620099</v>
+        <v>620267</v>
       </c>
       <c r="R9" t="n">
-        <v>6898937</v>
+        <v>6898931</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133623455</v>
+        <v>133623410</v>
       </c>
       <c r="B10" t="n">
-        <v>91881</v>
+        <v>79365</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620268</v>
+        <v>620159</v>
       </c>
       <c r="R10" t="n">
-        <v>6898926</v>
+        <v>6898960</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -2446,10 +2446,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133623465</v>
+        <v>133623448</v>
       </c>
       <c r="B20" t="n">
-        <v>79952</v>
+        <v>57958</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2457,37 +2457,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620113</v>
+        <v>620324</v>
       </c>
       <c r="R20" t="n">
-        <v>6898932</v>
+        <v>6898861</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2517,6 +2522,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2543,10 +2553,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133623443</v>
+        <v>133623465</v>
       </c>
       <c r="B21" t="n">
-        <v>79333</v>
+        <v>79952</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2554,21 +2564,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2578,10 +2588,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620349</v>
+        <v>620113</v>
       </c>
       <c r="R21" t="n">
-        <v>6898850</v>
+        <v>6898932</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2640,7 +2650,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133623423</v>
+        <v>133623443</v>
       </c>
       <c r="B22" t="n">
         <v>79333</v>
@@ -2675,10 +2685,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620235</v>
+        <v>620349</v>
       </c>
       <c r="R22" t="n">
-        <v>6898952</v>
+        <v>6898850</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2737,10 +2747,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133623448</v>
+        <v>133623423</v>
       </c>
       <c r="B23" t="n">
-        <v>57958</v>
+        <v>79333</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,42 +2758,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620324</v>
+        <v>620235</v>
       </c>
       <c r="R23" t="n">
-        <v>6898861</v>
+        <v>6898952</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2813,11 +2818,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2844,10 +2844,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133623422</v>
+        <v>133623444</v>
       </c>
       <c r="B24" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2855,21 +2855,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620275</v>
+        <v>620341</v>
       </c>
       <c r="R24" t="n">
-        <v>6898953</v>
+        <v>6898817</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133623444</v>
+        <v>133623422</v>
       </c>
       <c r="B25" t="n">
-        <v>91918</v>
+        <v>80438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2952,21 +2952,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620341</v>
+        <v>620275</v>
       </c>
       <c r="R25" t="n">
-        <v>6898817</v>
+        <v>6898953</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -5204,10 +5204,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133623453</v>
+        <v>133623417</v>
       </c>
       <c r="B48" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5215,21 +5215,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620262</v>
+        <v>620220</v>
       </c>
       <c r="R48" t="n">
-        <v>6898935</v>
+        <v>6898975</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5301,10 +5301,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133623417</v>
+        <v>133623453</v>
       </c>
       <c r="B49" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5312,21 +5312,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>620220</v>
+        <v>620262</v>
       </c>
       <c r="R49" t="n">
-        <v>6898975</v>
+        <v>6898935</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -869,53 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133623460</v>
+        <v>133623415</v>
       </c>
       <c r="B4" t="n">
-        <v>57958</v>
+        <v>91881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620244</v>
+        <v>620235</v>
       </c>
       <c r="R4" t="n">
-        <v>6898934</v>
+        <v>6898961</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -945,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,48 +966,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133623415</v>
+        <v>133623460</v>
       </c>
       <c r="B5" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620235</v>
+        <v>620244</v>
       </c>
       <c r="R5" t="n">
-        <v>6898961</v>
+        <v>6898934</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1047,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133623403</v>
+        <v>133623435</v>
       </c>
       <c r="B6" t="n">
-        <v>79333</v>
+        <v>79365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620099</v>
+        <v>620315</v>
       </c>
       <c r="R6" t="n">
-        <v>6898937</v>
+        <v>6899013</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133623455</v>
+        <v>133623430</v>
       </c>
       <c r="B7" t="n">
-        <v>91881</v>
+        <v>79365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620268</v>
+        <v>620267</v>
       </c>
       <c r="R7" t="n">
-        <v>6898926</v>
+        <v>6898931</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1267,7 +1267,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133623435</v>
+        <v>133623410</v>
       </c>
       <c r="B8" t="n">
         <v>79365</v>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620315</v>
+        <v>620159</v>
       </c>
       <c r="R8" t="n">
-        <v>6899013</v>
+        <v>6898960</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133623430</v>
+        <v>133623403</v>
       </c>
       <c r="B9" t="n">
-        <v>79365</v>
+        <v>79333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620267</v>
+        <v>620099</v>
       </c>
       <c r="R9" t="n">
-        <v>6898931</v>
+        <v>6898937</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133623410</v>
+        <v>133623455</v>
       </c>
       <c r="B10" t="n">
-        <v>79365</v>
+        <v>91881</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620159</v>
+        <v>620268</v>
       </c>
       <c r="R10" t="n">
-        <v>6898960</v>
+        <v>6898926</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -2446,10 +2446,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133623448</v>
+        <v>133623465</v>
       </c>
       <c r="B20" t="n">
-        <v>57958</v>
+        <v>79952</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2457,42 +2457,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620324</v>
+        <v>620113</v>
       </c>
       <c r="R20" t="n">
-        <v>6898861</v>
+        <v>6898932</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2522,11 +2517,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2553,10 +2543,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133623465</v>
+        <v>133623443</v>
       </c>
       <c r="B21" t="n">
-        <v>79952</v>
+        <v>79333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2564,21 +2554,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2588,10 +2578,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620113</v>
+        <v>620349</v>
       </c>
       <c r="R21" t="n">
-        <v>6898932</v>
+        <v>6898850</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2650,7 +2640,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133623443</v>
+        <v>133623423</v>
       </c>
       <c r="B22" t="n">
         <v>79333</v>
@@ -2685,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620349</v>
+        <v>620235</v>
       </c>
       <c r="R22" t="n">
-        <v>6898850</v>
+        <v>6898952</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2747,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133623423</v>
+        <v>133623448</v>
       </c>
       <c r="B23" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2758,37 +2748,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620235</v>
+        <v>620324</v>
       </c>
       <c r="R23" t="n">
-        <v>6898952</v>
+        <v>6898861</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2818,6 +2813,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -3135,32 +3135,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133623426</v>
+        <v>133623458</v>
       </c>
       <c r="B27" t="n">
-        <v>91881</v>
+        <v>91918</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620174</v>
+        <v>620239</v>
       </c>
       <c r="R27" t="n">
-        <v>6898936</v>
+        <v>6898916</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3232,10 +3232,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133623402</v>
+        <v>133623463</v>
       </c>
       <c r="B28" t="n">
-        <v>57958</v>
+        <v>92649</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3243,31 +3243,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>757</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3275,13 +3270,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620109</v>
+        <v>620142</v>
       </c>
       <c r="R28" t="n">
-        <v>6898948</v>
+        <v>6898946</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3313,12 +3308,18 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3337,53 +3338,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133623446</v>
+        <v>133623426</v>
       </c>
       <c r="B29" t="n">
-        <v>57958</v>
+        <v>91881</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620339</v>
+        <v>620174</v>
       </c>
       <c r="R29" t="n">
-        <v>6898847</v>
+        <v>6898936</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3439,10 +3435,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133623458</v>
+        <v>133623402</v>
       </c>
       <c r="B30" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3450,37 +3446,45 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620239</v>
+        <v>620109</v>
       </c>
       <c r="R30" t="n">
-        <v>6898916</v>
+        <v>6898948</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3536,10 +3540,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133623463</v>
+        <v>133623446</v>
       </c>
       <c r="B31" t="n">
-        <v>92649</v>
+        <v>57958</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3547,40 +3551,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>757</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620142</v>
+        <v>620339</v>
       </c>
       <c r="R31" t="n">
-        <v>6898946</v>
+        <v>6898847</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3612,18 +3618,12 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4132,32 +4132,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133623421</v>
+        <v>133623432</v>
       </c>
       <c r="B37" t="n">
-        <v>79365</v>
+        <v>91881</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620249</v>
+        <v>620266</v>
       </c>
       <c r="R37" t="n">
-        <v>6898992</v>
+        <v>6898927</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4229,32 +4229,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133623432</v>
+        <v>133623421</v>
       </c>
       <c r="B38" t="n">
-        <v>91881</v>
+        <v>79365</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4264,10 +4264,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>620266</v>
+        <v>620249</v>
       </c>
       <c r="R38" t="n">
-        <v>6898927</v>
+        <v>6898992</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5204,10 +5204,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133623417</v>
+        <v>133623453</v>
       </c>
       <c r="B48" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5215,21 +5215,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620220</v>
+        <v>620262</v>
       </c>
       <c r="R48" t="n">
-        <v>6898975</v>
+        <v>6898935</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5301,10 +5301,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133623453</v>
+        <v>133623417</v>
       </c>
       <c r="B49" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5312,21 +5312,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>620262</v>
+        <v>620220</v>
       </c>
       <c r="R49" t="n">
-        <v>6898935</v>
+        <v>6898975</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3135,32 +3135,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133623458</v>
+        <v>133623426</v>
       </c>
       <c r="B27" t="n">
-        <v>91918</v>
+        <v>91881</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620239</v>
+        <v>620174</v>
       </c>
       <c r="R27" t="n">
-        <v>6898916</v>
+        <v>6898936</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3232,10 +3232,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133623463</v>
+        <v>133623402</v>
       </c>
       <c r="B28" t="n">
-        <v>92649</v>
+        <v>57958</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3243,26 +3243,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>757</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3270,13 +3275,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620142</v>
+        <v>620109</v>
       </c>
       <c r="R28" t="n">
-        <v>6898946</v>
+        <v>6898948</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3308,18 +3313,12 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3338,48 +3337,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133623426</v>
+        <v>133623446</v>
       </c>
       <c r="B29" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620174</v>
+        <v>620339</v>
       </c>
       <c r="R29" t="n">
-        <v>6898936</v>
+        <v>6898847</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3435,10 +3439,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133623402</v>
+        <v>133623458</v>
       </c>
       <c r="B30" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3446,45 +3450,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620109</v>
+        <v>620239</v>
       </c>
       <c r="R30" t="n">
-        <v>6898948</v>
+        <v>6898916</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3540,10 +3536,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133623446</v>
+        <v>133623463</v>
       </c>
       <c r="B31" t="n">
-        <v>57958</v>
+        <v>92649</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3551,42 +3547,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>757</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620339</v>
+        <v>620142</v>
       </c>
       <c r="R31" t="n">
-        <v>6898847</v>
+        <v>6898946</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3618,12 +3612,18 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -5398,10 +5398,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133623466</v>
+        <v>133623456</v>
       </c>
       <c r="B50" t="n">
-        <v>91939</v>
+        <v>91918</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5409,21 +5409,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5433,10 +5433,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>620116</v>
+        <v>620264</v>
       </c>
       <c r="R50" t="n">
-        <v>6898986</v>
+        <v>6898924</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5495,10 +5495,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133623456</v>
+        <v>133623466</v>
       </c>
       <c r="B51" t="n">
-        <v>91918</v>
+        <v>91939</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5506,21 +5506,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>620264</v>
+        <v>620116</v>
       </c>
       <c r="R51" t="n">
-        <v>6898924</v>
+        <v>6898986</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5589,6 +5589,119 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>133815458</v>
+      </c>
+      <c r="B52" t="n">
+        <v>58119</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Långberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>620217</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6898924</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133623413</v>
+        <v>133623415</v>
       </c>
       <c r="B2" t="n">
-        <v>79333</v>
+        <v>91883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620178</v>
+        <v>620235</v>
       </c>
       <c r="R2" t="n">
-        <v>6898953</v>
+        <v>6898961</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133623447</v>
+        <v>133623460</v>
       </c>
       <c r="B3" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620318</v>
+        <v>620244</v>
       </c>
       <c r="R3" t="n">
-        <v>6898875</v>
+        <v>6898934</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -843,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133623415</v>
+        <v>133623413</v>
       </c>
       <c r="B4" t="n">
-        <v>91881</v>
+        <v>79334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620235</v>
+        <v>620178</v>
       </c>
       <c r="R4" t="n">
-        <v>6898961</v>
+        <v>6898953</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133623460</v>
+        <v>133623447</v>
       </c>
       <c r="B5" t="n">
-        <v>57958</v>
+        <v>79334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,42 +987,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620244</v>
+        <v>620318</v>
       </c>
       <c r="R5" t="n">
-        <v>6898934</v>
+        <v>6898875</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1042,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133623435</v>
+        <v>133623403</v>
       </c>
       <c r="B6" t="n">
-        <v>79365</v>
+        <v>79334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620315</v>
+        <v>620099</v>
       </c>
       <c r="R6" t="n">
-        <v>6899013</v>
+        <v>6898937</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133623430</v>
+        <v>133623455</v>
       </c>
       <c r="B7" t="n">
-        <v>79365</v>
+        <v>91883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620267</v>
+        <v>620268</v>
       </c>
       <c r="R7" t="n">
-        <v>6898931</v>
+        <v>6898926</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133623410</v>
+        <v>133623435</v>
       </c>
       <c r="B8" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620159</v>
+        <v>620315</v>
       </c>
       <c r="R8" t="n">
-        <v>6898960</v>
+        <v>6899013</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133623403</v>
+        <v>133623430</v>
       </c>
       <c r="B9" t="n">
-        <v>79333</v>
+        <v>79366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620099</v>
+        <v>620267</v>
       </c>
       <c r="R9" t="n">
-        <v>6898937</v>
+        <v>6898931</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133623455</v>
+        <v>133623410</v>
       </c>
       <c r="B10" t="n">
-        <v>91881</v>
+        <v>79366</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620268</v>
+        <v>620159</v>
       </c>
       <c r="R10" t="n">
-        <v>6898926</v>
+        <v>6898960</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1561,7 +1561,7 @@
         <v>133623407</v>
       </c>
       <c r="B11" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133623429</v>
+        <v>133623409</v>
       </c>
       <c r="B13" t="n">
-        <v>91918</v>
+        <v>79924</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620275</v>
+        <v>620161</v>
       </c>
       <c r="R13" t="n">
-        <v>6898905</v>
+        <v>6898969</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133623409</v>
+        <v>133623429</v>
       </c>
       <c r="B14" t="n">
-        <v>79923</v>
+        <v>91920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620161</v>
+        <v>620275</v>
       </c>
       <c r="R14" t="n">
-        <v>6898969</v>
+        <v>6898905</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1954,7 +1954,7 @@
         <v>133623436</v>
       </c>
       <c r="B15" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>133623434</v>
       </c>
       <c r="B16" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133623411</v>
+        <v>133623431</v>
       </c>
       <c r="B17" t="n">
-        <v>79365</v>
+        <v>79334</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620166</v>
+        <v>620266</v>
       </c>
       <c r="R17" t="n">
-        <v>6898962</v>
+        <v>6898928</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2242,45 +2242,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133623431</v>
+        <v>133623442</v>
       </c>
       <c r="B18" t="n">
-        <v>79333</v>
+        <v>4775</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620266</v>
+        <v>620347</v>
       </c>
       <c r="R18" t="n">
-        <v>6898928</v>
+        <v>6898852</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2321,6 +2330,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2339,54 +2349,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133623442</v>
+        <v>133623411</v>
       </c>
       <c r="B19" t="n">
-        <v>4775</v>
+        <v>79366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100299</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620347</v>
+        <v>620166</v>
       </c>
       <c r="R19" t="n">
-        <v>6898852</v>
+        <v>6898962</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2427,7 +2428,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2446,10 +2446,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133623465</v>
+        <v>133623448</v>
       </c>
       <c r="B20" t="n">
-        <v>79952</v>
+        <v>57958</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2457,37 +2457,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620113</v>
+        <v>620324</v>
       </c>
       <c r="R20" t="n">
-        <v>6898932</v>
+        <v>6898861</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2517,6 +2522,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2543,10 +2553,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133623443</v>
+        <v>133623465</v>
       </c>
       <c r="B21" t="n">
-        <v>79333</v>
+        <v>79953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2554,21 +2564,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2578,10 +2588,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620349</v>
+        <v>620113</v>
       </c>
       <c r="R21" t="n">
-        <v>6898850</v>
+        <v>6898932</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2640,10 +2650,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133623423</v>
+        <v>133623443</v>
       </c>
       <c r="B22" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2675,10 +2685,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620235</v>
+        <v>620349</v>
       </c>
       <c r="R22" t="n">
-        <v>6898952</v>
+        <v>6898850</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2737,10 +2747,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133623448</v>
+        <v>133623423</v>
       </c>
       <c r="B23" t="n">
-        <v>57958</v>
+        <v>79334</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,42 +2758,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620324</v>
+        <v>620235</v>
       </c>
       <c r="R23" t="n">
-        <v>6898861</v>
+        <v>6898952</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2813,11 +2818,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2844,32 +2844,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133623444</v>
+        <v>133623452</v>
       </c>
       <c r="B24" t="n">
-        <v>91918</v>
+        <v>91883</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620341</v>
+        <v>620384</v>
       </c>
       <c r="R24" t="n">
-        <v>6898817</v>
+        <v>6898898</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133623422</v>
+        <v>133623444</v>
       </c>
       <c r="B25" t="n">
-        <v>80438</v>
+        <v>91920</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2952,21 +2952,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620275</v>
+        <v>620341</v>
       </c>
       <c r="R25" t="n">
-        <v>6898953</v>
+        <v>6898817</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3038,32 +3038,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133623452</v>
+        <v>133623422</v>
       </c>
       <c r="B26" t="n">
-        <v>91881</v>
+        <v>80439</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620384</v>
+        <v>620275</v>
       </c>
       <c r="R26" t="n">
-        <v>6898898</v>
+        <v>6898953</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3135,48 +3135,56 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133623426</v>
+        <v>133623402</v>
       </c>
       <c r="B27" t="n">
-        <v>91881</v>
+        <v>57958</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620174</v>
+        <v>620109</v>
       </c>
       <c r="R27" t="n">
-        <v>6898936</v>
+        <v>6898948</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3232,7 +3240,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133623402</v>
+        <v>133623446</v>
       </c>
       <c r="B28" t="n">
         <v>57958</v>
@@ -3261,24 +3269,21 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620109</v>
+        <v>620339</v>
       </c>
       <c r="R28" t="n">
-        <v>6898948</v>
+        <v>6898847</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3337,10 +3342,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133623446</v>
+        <v>133623458</v>
       </c>
       <c r="B29" t="n">
-        <v>57958</v>
+        <v>91920</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3348,42 +3353,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620339</v>
+        <v>620239</v>
       </c>
       <c r="R29" t="n">
-        <v>6898847</v>
+        <v>6898916</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133623458</v>
+        <v>133623463</v>
       </c>
       <c r="B30" t="n">
-        <v>91918</v>
+        <v>92651</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3450,34 +3450,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>757</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620239</v>
+        <v>620142</v>
       </c>
       <c r="R30" t="n">
-        <v>6898916</v>
+        <v>6898946</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3512,12 +3515,18 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3536,48 +3545,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133623463</v>
+        <v>133623426</v>
       </c>
       <c r="B31" t="n">
-        <v>92649</v>
+        <v>91883</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>757</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620142</v>
+        <v>620174</v>
       </c>
       <c r="R31" t="n">
-        <v>6898946</v>
+        <v>6898936</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3612,18 +3618,12 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3645,7 +3645,7 @@
         <v>133623462</v>
       </c>
       <c r="B32" t="n">
-        <v>92649</v>
+        <v>92651</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3744,10 +3744,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133623433</v>
+        <v>133623459</v>
       </c>
       <c r="B33" t="n">
-        <v>83307</v>
+        <v>81319</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3755,21 +3755,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>1049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3779,10 +3779,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620290</v>
+        <v>620266</v>
       </c>
       <c r="R33" t="n">
-        <v>6898929</v>
+        <v>6898988</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3841,32 +3841,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133623438</v>
+        <v>133623464</v>
       </c>
       <c r="B34" t="n">
-        <v>78999</v>
+        <v>91883</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3876,10 +3876,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>620335</v>
+        <v>620127</v>
       </c>
       <c r="R34" t="n">
-        <v>6898933</v>
+        <v>6898927</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3938,10 +3938,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133623459</v>
+        <v>133623433</v>
       </c>
       <c r="B35" t="n">
-        <v>81318</v>
+        <v>83308</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3949,21 +3949,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1049</v>
+        <v>308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3973,10 +3973,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>620266</v>
+        <v>620290</v>
       </c>
       <c r="R35" t="n">
-        <v>6898988</v>
+        <v>6898929</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4035,32 +4035,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133623464</v>
+        <v>133623438</v>
       </c>
       <c r="B36" t="n">
-        <v>91881</v>
+        <v>79000</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620127</v>
+        <v>620335</v>
       </c>
       <c r="R36" t="n">
-        <v>6898927</v>
+        <v>6898933</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4132,32 +4132,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133623432</v>
+        <v>133623421</v>
       </c>
       <c r="B37" t="n">
-        <v>91881</v>
+        <v>79366</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620266</v>
+        <v>620249</v>
       </c>
       <c r="R37" t="n">
-        <v>6898927</v>
+        <v>6898992</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4229,32 +4229,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133623421</v>
+        <v>133623432</v>
       </c>
       <c r="B38" t="n">
-        <v>79365</v>
+        <v>91883</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4264,10 +4264,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>620249</v>
+        <v>620266</v>
       </c>
       <c r="R38" t="n">
-        <v>6898992</v>
+        <v>6898927</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4329,7 +4329,7 @@
         <v>133623437</v>
       </c>
       <c r="B39" t="n">
-        <v>79952</v>
+        <v>79953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4525,10 +4525,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133623404</v>
+        <v>133623428</v>
       </c>
       <c r="B41" t="n">
-        <v>79365</v>
+        <v>91920</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4536,21 +4536,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>620098</v>
+        <v>620196</v>
       </c>
       <c r="R41" t="n">
-        <v>6898939</v>
+        <v>6898931</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4622,10 +4622,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133623428</v>
+        <v>133623404</v>
       </c>
       <c r="B42" t="n">
-        <v>91918</v>
+        <v>79366</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4633,21 +4633,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4657,10 +4657,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620196</v>
+        <v>620098</v>
       </c>
       <c r="R42" t="n">
-        <v>6898931</v>
+        <v>6898939</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4722,7 +4722,7 @@
         <v>133623424</v>
       </c>
       <c r="B43" t="n">
-        <v>79952</v>
+        <v>79953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>133623412</v>
       </c>
       <c r="B44" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>133623439</v>
       </c>
       <c r="B45" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>133623425</v>
       </c>
       <c r="B46" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>133623445</v>
       </c>
       <c r="B47" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5204,10 +5204,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133623453</v>
+        <v>133623417</v>
       </c>
       <c r="B48" t="n">
-        <v>79333</v>
+        <v>80439</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5215,21 +5215,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620262</v>
+        <v>620220</v>
       </c>
       <c r="R48" t="n">
-        <v>6898935</v>
+        <v>6898975</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5301,10 +5301,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133623417</v>
+        <v>133623453</v>
       </c>
       <c r="B49" t="n">
-        <v>80438</v>
+        <v>79334</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5312,21 +5312,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>620220</v>
+        <v>620262</v>
       </c>
       <c r="R49" t="n">
-        <v>6898975</v>
+        <v>6898935</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5401,7 +5401,7 @@
         <v>133623456</v>
       </c>
       <c r="B50" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>133623466</v>
       </c>
       <c r="B51" t="n">
-        <v>91939</v>
+        <v>91941</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -2446,10 +2446,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133623448</v>
+        <v>133623465</v>
       </c>
       <c r="B20" t="n">
-        <v>57958</v>
+        <v>79953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2457,42 +2457,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620324</v>
+        <v>620113</v>
       </c>
       <c r="R20" t="n">
-        <v>6898861</v>
+        <v>6898932</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2522,11 +2517,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2553,10 +2543,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133623465</v>
+        <v>133623443</v>
       </c>
       <c r="B21" t="n">
-        <v>79953</v>
+        <v>79334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2564,21 +2554,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2588,10 +2578,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620113</v>
+        <v>620349</v>
       </c>
       <c r="R21" t="n">
-        <v>6898932</v>
+        <v>6898850</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2650,7 +2640,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133623443</v>
+        <v>133623423</v>
       </c>
       <c r="B22" t="n">
         <v>79334</v>
@@ -2685,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620349</v>
+        <v>620235</v>
       </c>
       <c r="R22" t="n">
-        <v>6898850</v>
+        <v>6898952</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2747,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133623423</v>
+        <v>133623448</v>
       </c>
       <c r="B23" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2758,37 +2748,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620235</v>
+        <v>620324</v>
       </c>
       <c r="R23" t="n">
-        <v>6898952</v>
+        <v>6898861</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2818,6 +2813,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2844,32 +2844,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133623452</v>
+        <v>133623444</v>
       </c>
       <c r="B24" t="n">
-        <v>91883</v>
+        <v>91920</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620384</v>
+        <v>620341</v>
       </c>
       <c r="R24" t="n">
-        <v>6898898</v>
+        <v>6898817</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133623444</v>
+        <v>133623422</v>
       </c>
       <c r="B25" t="n">
-        <v>91920</v>
+        <v>80439</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2952,21 +2952,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620341</v>
+        <v>620275</v>
       </c>
       <c r="R25" t="n">
-        <v>6898817</v>
+        <v>6898953</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3038,32 +3038,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133623422</v>
+        <v>133623452</v>
       </c>
       <c r="B26" t="n">
-        <v>80439</v>
+        <v>91883</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620275</v>
+        <v>620384</v>
       </c>
       <c r="R26" t="n">
-        <v>6898953</v>
+        <v>6898898</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133623462</v>
+        <v>133623433</v>
       </c>
       <c r="B32" t="n">
-        <v>92651</v>
+        <v>83308</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3653,21 +3653,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>757</v>
+        <v>308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620130</v>
+        <v>620290</v>
       </c>
       <c r="R32" t="n">
-        <v>6898930</v>
+        <v>6898929</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3713,11 +3713,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar. Röd KOH-reaktion</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3744,10 +3739,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133623459</v>
+        <v>133623438</v>
       </c>
       <c r="B33" t="n">
-        <v>81319</v>
+        <v>79000</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3755,21 +3750,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3779,10 +3774,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620266</v>
+        <v>620335</v>
       </c>
       <c r="R33" t="n">
-        <v>6898988</v>
+        <v>6898933</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3938,10 +3933,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133623433</v>
+        <v>133623462</v>
       </c>
       <c r="B35" t="n">
-        <v>83308</v>
+        <v>92651</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3949,21 +3944,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>308</v>
+        <v>757</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3973,10 +3968,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>620290</v>
+        <v>620130</v>
       </c>
       <c r="R35" t="n">
-        <v>6898929</v>
+        <v>6898930</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4009,6 +4004,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar. Röd KOH-reaktion</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4035,10 +4035,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133623438</v>
+        <v>133623459</v>
       </c>
       <c r="B36" t="n">
-        <v>79000</v>
+        <v>81319</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4046,21 +4046,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620335</v>
+        <v>620266</v>
       </c>
       <c r="R36" t="n">
-        <v>6898933</v>
+        <v>6898988</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4525,10 +4525,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133623428</v>
+        <v>133623404</v>
       </c>
       <c r="B41" t="n">
-        <v>91920</v>
+        <v>79366</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4536,21 +4536,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>620196</v>
+        <v>620098</v>
       </c>
       <c r="R41" t="n">
-        <v>6898931</v>
+        <v>6898939</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4622,10 +4622,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133623404</v>
+        <v>133623428</v>
       </c>
       <c r="B42" t="n">
-        <v>79366</v>
+        <v>91920</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4633,21 +4633,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4657,10 +4657,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620098</v>
+        <v>620196</v>
       </c>
       <c r="R42" t="n">
-        <v>6898939</v>
+        <v>6898931</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5398,10 +5398,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133623456</v>
+        <v>133623466</v>
       </c>
       <c r="B50" t="n">
-        <v>91920</v>
+        <v>91941</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5409,21 +5409,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5433,10 +5433,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>620264</v>
+        <v>620116</v>
       </c>
       <c r="R50" t="n">
-        <v>6898924</v>
+        <v>6898986</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5495,10 +5495,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133623466</v>
+        <v>133623456</v>
       </c>
       <c r="B51" t="n">
-        <v>91941</v>
+        <v>91920</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5506,21 +5506,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>620116</v>
+        <v>620264</v>
       </c>
       <c r="R51" t="n">
-        <v>6898986</v>
+        <v>6898924</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133623460</v>
+        <v>133623413</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>79334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620244</v>
+        <v>620178</v>
       </c>
       <c r="R3" t="n">
-        <v>6898934</v>
+        <v>6898953</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -848,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133623413</v>
+        <v>133623447</v>
       </c>
       <c r="B4" t="n">
         <v>79334</v>
@@ -914,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620178</v>
+        <v>620318</v>
       </c>
       <c r="R4" t="n">
-        <v>6898953</v>
+        <v>6898875</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -976,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133623447</v>
+        <v>133623460</v>
       </c>
       <c r="B5" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,37 +977,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620318</v>
+        <v>620244</v>
       </c>
       <c r="R5" t="n">
-        <v>6898875</v>
+        <v>6898934</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1047,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133623409</v>
+        <v>133623429</v>
       </c>
       <c r="B13" t="n">
-        <v>79924</v>
+        <v>91920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620161</v>
+        <v>620275</v>
       </c>
       <c r="R13" t="n">
-        <v>6898969</v>
+        <v>6898905</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133623429</v>
+        <v>133623409</v>
       </c>
       <c r="B14" t="n">
-        <v>91920</v>
+        <v>79924</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620275</v>
+        <v>620161</v>
       </c>
       <c r="R14" t="n">
-        <v>6898905</v>
+        <v>6898969</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133623431</v>
+        <v>133623411</v>
       </c>
       <c r="B17" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620266</v>
+        <v>620166</v>
       </c>
       <c r="R17" t="n">
-        <v>6898928</v>
+        <v>6898962</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2242,54 +2242,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133623442</v>
+        <v>133623431</v>
       </c>
       <c r="B18" t="n">
-        <v>4775</v>
+        <v>79334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620347</v>
+        <v>620266</v>
       </c>
       <c r="R18" t="n">
-        <v>6898852</v>
+        <v>6898928</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2330,7 +2321,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2349,45 +2339,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133623411</v>
+        <v>133623442</v>
       </c>
       <c r="B19" t="n">
-        <v>79366</v>
+        <v>4775</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>100299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620166</v>
+        <v>620347</v>
       </c>
       <c r="R19" t="n">
-        <v>6898962</v>
+        <v>6898852</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2428,6 +2427,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133623433</v>
+        <v>133623462</v>
       </c>
       <c r="B32" t="n">
-        <v>83308</v>
+        <v>92651</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3653,21 +3653,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>757</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620290</v>
+        <v>620130</v>
       </c>
       <c r="R32" t="n">
-        <v>6898929</v>
+        <v>6898930</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3713,6 +3713,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar. Röd KOH-reaktion</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3739,10 +3744,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133623438</v>
+        <v>133623459</v>
       </c>
       <c r="B33" t="n">
-        <v>79000</v>
+        <v>81319</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3750,21 +3755,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3774,10 +3779,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620335</v>
+        <v>620266</v>
       </c>
       <c r="R33" t="n">
-        <v>6898933</v>
+        <v>6898988</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3933,10 +3938,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133623462</v>
+        <v>133623433</v>
       </c>
       <c r="B35" t="n">
-        <v>92651</v>
+        <v>83308</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3944,21 +3949,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>757</v>
+        <v>308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3968,10 +3973,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>620130</v>
+        <v>620290</v>
       </c>
       <c r="R35" t="n">
-        <v>6898930</v>
+        <v>6898929</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4004,11 +4009,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar. Röd KOH-reaktion</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4035,10 +4035,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133623459</v>
+        <v>133623438</v>
       </c>
       <c r="B36" t="n">
-        <v>81319</v>
+        <v>79000</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4046,21 +4046,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620266</v>
+        <v>620335</v>
       </c>
       <c r="R36" t="n">
-        <v>6898988</v>
+        <v>6898933</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4622,10 +4622,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133623428</v>
+        <v>133623424</v>
       </c>
       <c r="B42" t="n">
-        <v>91920</v>
+        <v>79953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4633,21 +4633,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4657,10 +4657,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620196</v>
+        <v>620238</v>
       </c>
       <c r="R42" t="n">
-        <v>6898931</v>
+        <v>6898939</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4719,10 +4719,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133623424</v>
+        <v>133623428</v>
       </c>
       <c r="B43" t="n">
-        <v>79953</v>
+        <v>91920</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4730,21 +4730,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4754,10 +4754,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620238</v>
+        <v>620196</v>
       </c>
       <c r="R43" t="n">
-        <v>6898939</v>
+        <v>6898931</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133623415</v>
       </c>
       <c r="B2" t="n">
-        <v>91883</v>
+        <v>91891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>133623455</v>
       </c>
       <c r="B7" t="n">
-        <v>91883</v>
+        <v>91891</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133623435</v>
+        <v>133623430</v>
       </c>
       <c r="B8" t="n">
         <v>79366</v>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620315</v>
+        <v>620267</v>
       </c>
       <c r="R8" t="n">
-        <v>6899013</v>
+        <v>6898931</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133623430</v>
+        <v>133623410</v>
       </c>
       <c r="B9" t="n">
         <v>79366</v>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620267</v>
+        <v>620159</v>
       </c>
       <c r="R9" t="n">
-        <v>6898931</v>
+        <v>6898960</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1461,7 +1461,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133623410</v>
+        <v>133623435</v>
       </c>
       <c r="B10" t="n">
         <v>79366</v>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620159</v>
+        <v>620315</v>
       </c>
       <c r="R10" t="n">
-        <v>6898960</v>
+        <v>6899013</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133623429</v>
+        <v>133623409</v>
       </c>
       <c r="B13" t="n">
-        <v>91920</v>
+        <v>79924</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620275</v>
+        <v>620161</v>
       </c>
       <c r="R13" t="n">
-        <v>6898905</v>
+        <v>6898969</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133623409</v>
+        <v>133623429</v>
       </c>
       <c r="B14" t="n">
-        <v>79924</v>
+        <v>91928</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620161</v>
+        <v>620275</v>
       </c>
       <c r="R14" t="n">
-        <v>6898969</v>
+        <v>6898905</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1954,7 +1954,7 @@
         <v>133623436</v>
       </c>
       <c r="B15" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>133623434</v>
       </c>
       <c r="B16" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>133623444</v>
       </c>
       <c r="B24" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2941,32 +2941,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133623422</v>
+        <v>133623452</v>
       </c>
       <c r="B25" t="n">
-        <v>80439</v>
+        <v>91891</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620275</v>
+        <v>620384</v>
       </c>
       <c r="R25" t="n">
-        <v>6898953</v>
+        <v>6898898</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3038,32 +3038,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133623452</v>
+        <v>133623422</v>
       </c>
       <c r="B26" t="n">
-        <v>91883</v>
+        <v>80439</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620384</v>
+        <v>620275</v>
       </c>
       <c r="R26" t="n">
-        <v>6898898</v>
+        <v>6898953</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3342,10 +3342,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133623458</v>
+        <v>133623463</v>
       </c>
       <c r="B29" t="n">
-        <v>91920</v>
+        <v>92659</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3353,34 +3353,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>757</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620239</v>
+        <v>620142</v>
       </c>
       <c r="R29" t="n">
-        <v>6898916</v>
+        <v>6898946</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3415,12 +3418,18 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3439,10 +3448,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133623463</v>
+        <v>133623458</v>
       </c>
       <c r="B30" t="n">
-        <v>92651</v>
+        <v>91928</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3450,37 +3459,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>757</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620142</v>
+        <v>620239</v>
       </c>
       <c r="R30" t="n">
-        <v>6898946</v>
+        <v>6898916</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3515,18 +3521,12 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>133623426</v>
       </c>
       <c r="B31" t="n">
-        <v>91883</v>
+        <v>91891</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>133623462</v>
       </c>
       <c r="B32" t="n">
-        <v>92651</v>
+        <v>92659</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3744,10 +3744,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133623459</v>
+        <v>133623438</v>
       </c>
       <c r="B33" t="n">
-        <v>81319</v>
+        <v>79000</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3755,21 +3755,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3779,10 +3779,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620266</v>
+        <v>620335</v>
       </c>
       <c r="R33" t="n">
-        <v>6898988</v>
+        <v>6898933</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3841,32 +3841,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133623464</v>
+        <v>133623433</v>
       </c>
       <c r="B34" t="n">
-        <v>91883</v>
+        <v>83311</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3876,10 +3876,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>620127</v>
+        <v>620290</v>
       </c>
       <c r="R34" t="n">
-        <v>6898927</v>
+        <v>6898929</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3938,10 +3938,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133623433</v>
+        <v>133623459</v>
       </c>
       <c r="B35" t="n">
-        <v>83308</v>
+        <v>81319</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3949,21 +3949,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>308</v>
+        <v>1049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3973,10 +3973,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>620290</v>
+        <v>620266</v>
       </c>
       <c r="R35" t="n">
-        <v>6898929</v>
+        <v>6898988</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4035,32 +4035,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133623438</v>
+        <v>133623464</v>
       </c>
       <c r="B36" t="n">
-        <v>79000</v>
+        <v>91891</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620335</v>
+        <v>620127</v>
       </c>
       <c r="R36" t="n">
-        <v>6898933</v>
+        <v>6898927</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4232,7 +4232,7 @@
         <v>133623432</v>
       </c>
       <c r="B38" t="n">
-        <v>91883</v>
+        <v>91891</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4326,10 +4326,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133623437</v>
+        <v>133623408</v>
       </c>
       <c r="B39" t="n">
-        <v>79953</v>
+        <v>57958</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4337,37 +4337,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>620340</v>
+        <v>620156</v>
       </c>
       <c r="R39" t="n">
-        <v>6898950</v>
+        <v>6898981</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4423,10 +4428,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133623408</v>
+        <v>133623437</v>
       </c>
       <c r="B40" t="n">
-        <v>57958</v>
+        <v>79953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4434,42 +4439,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>620156</v>
+        <v>620340</v>
       </c>
       <c r="R40" t="n">
-        <v>6898981</v>
+        <v>6898950</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4525,10 +4525,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133623404</v>
+        <v>133623428</v>
       </c>
       <c r="B41" t="n">
-        <v>79366</v>
+        <v>91928</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4536,21 +4536,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>620098</v>
+        <v>620196</v>
       </c>
       <c r="R41" t="n">
-        <v>6898939</v>
+        <v>6898931</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4622,10 +4622,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133623424</v>
+        <v>133623404</v>
       </c>
       <c r="B42" t="n">
-        <v>79953</v>
+        <v>79366</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4633,21 +4633,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620238</v>
+        <v>620098</v>
       </c>
       <c r="R42" t="n">
         <v>6898939</v>
@@ -4719,10 +4719,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133623428</v>
+        <v>133623424</v>
       </c>
       <c r="B43" t="n">
-        <v>91920</v>
+        <v>79953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4730,21 +4730,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4754,10 +4754,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620196</v>
+        <v>620238</v>
       </c>
       <c r="R43" t="n">
-        <v>6898931</v>
+        <v>6898939</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4816,7 +4816,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133623412</v>
+        <v>133623439</v>
       </c>
       <c r="B44" t="n">
         <v>79366</v>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>620162</v>
+        <v>620336</v>
       </c>
       <c r="R44" t="n">
-        <v>6899008</v>
+        <v>6898875</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4913,7 +4913,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133623439</v>
+        <v>133623412</v>
       </c>
       <c r="B45" t="n">
         <v>79366</v>
@@ -4948,10 +4948,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>620336</v>
+        <v>620162</v>
       </c>
       <c r="R45" t="n">
-        <v>6898875</v>
+        <v>6899008</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5013,7 +5013,7 @@
         <v>133623425</v>
       </c>
       <c r="B46" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>133623445</v>
       </c>
       <c r="B47" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5204,10 +5204,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133623417</v>
+        <v>133623453</v>
       </c>
       <c r="B48" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5215,21 +5215,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620220</v>
+        <v>620262</v>
       </c>
       <c r="R48" t="n">
-        <v>6898975</v>
+        <v>6898935</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5301,10 +5301,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133623453</v>
+        <v>133623417</v>
       </c>
       <c r="B49" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5312,21 +5312,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>620262</v>
+        <v>620220</v>
       </c>
       <c r="R49" t="n">
-        <v>6898935</v>
+        <v>6898975</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5398,10 +5398,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133623466</v>
+        <v>133623456</v>
       </c>
       <c r="B50" t="n">
-        <v>91941</v>
+        <v>91928</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5409,21 +5409,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5433,10 +5433,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>620116</v>
+        <v>620264</v>
       </c>
       <c r="R50" t="n">
-        <v>6898986</v>
+        <v>6898924</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5495,10 +5495,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133623456</v>
+        <v>133623466</v>
       </c>
       <c r="B51" t="n">
-        <v>91920</v>
+        <v>91949</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5506,21 +5506,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>620264</v>
+        <v>620116</v>
       </c>
       <c r="R51" t="n">
-        <v>6898924</v>
+        <v>6898986</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133623403</v>
+        <v>133623430</v>
       </c>
       <c r="B6" t="n">
-        <v>79334</v>
+        <v>79366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620099</v>
+        <v>620267</v>
       </c>
       <c r="R6" t="n">
-        <v>6898937</v>
+        <v>6898931</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133623455</v>
+        <v>133623410</v>
       </c>
       <c r="B7" t="n">
-        <v>91891</v>
+        <v>79366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620268</v>
+        <v>620159</v>
       </c>
       <c r="R7" t="n">
-        <v>6898926</v>
+        <v>6898960</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1267,7 +1267,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133623430</v>
+        <v>133623435</v>
       </c>
       <c r="B8" t="n">
         <v>79366</v>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620267</v>
+        <v>620315</v>
       </c>
       <c r="R8" t="n">
-        <v>6898931</v>
+        <v>6899013</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133623410</v>
+        <v>133623403</v>
       </c>
       <c r="B9" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620159</v>
+        <v>620099</v>
       </c>
       <c r="R9" t="n">
-        <v>6898960</v>
+        <v>6898937</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133623435</v>
+        <v>133623455</v>
       </c>
       <c r="B10" t="n">
-        <v>79366</v>
+        <v>91891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620315</v>
+        <v>620268</v>
       </c>
       <c r="R10" t="n">
-        <v>6899013</v>
+        <v>6898926</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -3642,32 +3642,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133623462</v>
+        <v>133623464</v>
       </c>
       <c r="B32" t="n">
-        <v>92659</v>
+        <v>91891</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>757</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620130</v>
+        <v>620127</v>
       </c>
       <c r="R32" t="n">
-        <v>6898930</v>
+        <v>6898927</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3713,11 +3713,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar. Röd KOH-reaktion</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3744,10 +3739,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133623438</v>
+        <v>133623462</v>
       </c>
       <c r="B33" t="n">
-        <v>79000</v>
+        <v>92659</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3755,21 +3750,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>757</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3779,10 +3774,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620335</v>
+        <v>620130</v>
       </c>
       <c r="R33" t="n">
-        <v>6898933</v>
+        <v>6898930</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3815,6 +3810,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar. Röd KOH-reaktion</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3841,10 +3841,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133623433</v>
+        <v>133623438</v>
       </c>
       <c r="B34" t="n">
-        <v>83311</v>
+        <v>79000</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3852,21 +3852,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>308</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3876,10 +3876,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>620290</v>
+        <v>620335</v>
       </c>
       <c r="R34" t="n">
-        <v>6898929</v>
+        <v>6898933</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3938,10 +3938,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133623459</v>
+        <v>133623433</v>
       </c>
       <c r="B35" t="n">
-        <v>81319</v>
+        <v>83311</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3949,21 +3949,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1049</v>
+        <v>308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3973,10 +3973,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>620266</v>
+        <v>620290</v>
       </c>
       <c r="R35" t="n">
-        <v>6898988</v>
+        <v>6898929</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4035,32 +4035,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133623464</v>
+        <v>133623459</v>
       </c>
       <c r="B36" t="n">
-        <v>91891</v>
+        <v>81319</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>1049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620127</v>
+        <v>620266</v>
       </c>
       <c r="R36" t="n">
-        <v>6898927</v>
+        <v>6898988</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4326,10 +4326,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133623408</v>
+        <v>133623437</v>
       </c>
       <c r="B39" t="n">
-        <v>57958</v>
+        <v>79953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4337,42 +4337,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>620156</v>
+        <v>620340</v>
       </c>
       <c r="R39" t="n">
-        <v>6898981</v>
+        <v>6898950</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4428,10 +4423,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133623437</v>
+        <v>133623408</v>
       </c>
       <c r="B40" t="n">
-        <v>79953</v>
+        <v>57958</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4439,37 +4434,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>620340</v>
+        <v>620156</v>
       </c>
       <c r="R40" t="n">
-        <v>6898950</v>
+        <v>6898981</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133623409</v>
+        <v>133623429</v>
       </c>
       <c r="B13" t="n">
-        <v>79924</v>
+        <v>91928</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620161</v>
+        <v>620275</v>
       </c>
       <c r="R13" t="n">
-        <v>6898969</v>
+        <v>6898905</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133623429</v>
+        <v>133623409</v>
       </c>
       <c r="B14" t="n">
-        <v>91928</v>
+        <v>79924</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620275</v>
+        <v>620161</v>
       </c>
       <c r="R14" t="n">
-        <v>6898905</v>
+        <v>6898969</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133623411</v>
+        <v>133623431</v>
       </c>
       <c r="B17" t="n">
-        <v>79366</v>
+        <v>79334</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620166</v>
+        <v>620266</v>
       </c>
       <c r="R17" t="n">
-        <v>6898962</v>
+        <v>6898928</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2242,45 +2242,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133623431</v>
+        <v>133623442</v>
       </c>
       <c r="B18" t="n">
-        <v>79334</v>
+        <v>4775</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620266</v>
+        <v>620347</v>
       </c>
       <c r="R18" t="n">
-        <v>6898928</v>
+        <v>6898852</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2321,6 +2330,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2339,54 +2349,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133623442</v>
+        <v>133623411</v>
       </c>
       <c r="B19" t="n">
-        <v>4775</v>
+        <v>79366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100299</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620347</v>
+        <v>620166</v>
       </c>
       <c r="R19" t="n">
-        <v>6898852</v>
+        <v>6898962</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2427,7 +2428,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3135,10 +3135,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133623402</v>
+        <v>133623463</v>
       </c>
       <c r="B27" t="n">
-        <v>57958</v>
+        <v>92659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3146,31 +3146,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>757</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3178,13 +3173,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620109</v>
+        <v>620142</v>
       </c>
       <c r="R27" t="n">
-        <v>6898948</v>
+        <v>6898946</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3216,12 +3211,18 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3240,10 +3241,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133623446</v>
+        <v>133623458</v>
       </c>
       <c r="B28" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3251,42 +3252,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620339</v>
+        <v>620239</v>
       </c>
       <c r="R28" t="n">
-        <v>6898847</v>
+        <v>6898916</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3342,48 +3338,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133623463</v>
+        <v>133623426</v>
       </c>
       <c r="B29" t="n">
-        <v>92659</v>
+        <v>91891</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>757</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620142</v>
+        <v>620174</v>
       </c>
       <c r="R29" t="n">
-        <v>6898946</v>
+        <v>6898936</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3418,18 +3411,12 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3448,10 +3435,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133623458</v>
+        <v>133623402</v>
       </c>
       <c r="B30" t="n">
-        <v>91928</v>
+        <v>57958</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3459,37 +3446,45 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620239</v>
+        <v>620109</v>
       </c>
       <c r="R30" t="n">
-        <v>6898916</v>
+        <v>6898948</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3545,48 +3540,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133623426</v>
+        <v>133623446</v>
       </c>
       <c r="B31" t="n">
-        <v>91891</v>
+        <v>57958</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620174</v>
+        <v>620339</v>
       </c>
       <c r="R31" t="n">
-        <v>6898936</v>
+        <v>6898847</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3642,32 +3642,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133623464</v>
+        <v>133623462</v>
       </c>
       <c r="B32" t="n">
-        <v>91891</v>
+        <v>92659</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>757</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620127</v>
+        <v>620130</v>
       </c>
       <c r="R32" t="n">
-        <v>6898927</v>
+        <v>6898930</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3713,6 +3713,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar. Röd KOH-reaktion</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3739,10 +3744,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133623462</v>
+        <v>133623438</v>
       </c>
       <c r="B33" t="n">
-        <v>92659</v>
+        <v>79000</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3750,21 +3755,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>757</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3774,10 +3779,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620130</v>
+        <v>620335</v>
       </c>
       <c r="R33" t="n">
-        <v>6898930</v>
+        <v>6898933</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3810,11 +3815,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar. Röd KOH-reaktion</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3841,10 +3841,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133623438</v>
+        <v>133623433</v>
       </c>
       <c r="B34" t="n">
-        <v>79000</v>
+        <v>83311</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3852,21 +3852,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3876,10 +3876,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>620335</v>
+        <v>620290</v>
       </c>
       <c r="R34" t="n">
-        <v>6898933</v>
+        <v>6898929</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3938,10 +3938,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133623433</v>
+        <v>133623459</v>
       </c>
       <c r="B35" t="n">
-        <v>83311</v>
+        <v>81319</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3949,21 +3949,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>308</v>
+        <v>1049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3973,10 +3973,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>620290</v>
+        <v>620266</v>
       </c>
       <c r="R35" t="n">
-        <v>6898929</v>
+        <v>6898988</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4035,32 +4035,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133623459</v>
+        <v>133623464</v>
       </c>
       <c r="B36" t="n">
-        <v>81319</v>
+        <v>91891</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1049</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620266</v>
+        <v>620127</v>
       </c>
       <c r="R36" t="n">
-        <v>6898988</v>
+        <v>6898927</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133623429</v>
+        <v>133623409</v>
       </c>
       <c r="B13" t="n">
-        <v>91928</v>
+        <v>79924</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620275</v>
+        <v>620161</v>
       </c>
       <c r="R13" t="n">
-        <v>6898905</v>
+        <v>6898969</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133623409</v>
+        <v>133623429</v>
       </c>
       <c r="B14" t="n">
-        <v>79924</v>
+        <v>91928</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620161</v>
+        <v>620275</v>
       </c>
       <c r="R14" t="n">
-        <v>6898969</v>
+        <v>6898905</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -3135,10 +3135,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133623463</v>
+        <v>133623402</v>
       </c>
       <c r="B27" t="n">
-        <v>92659</v>
+        <v>57958</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3146,26 +3146,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>757</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3173,13 +3178,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620142</v>
+        <v>620109</v>
       </c>
       <c r="R27" t="n">
-        <v>6898946</v>
+        <v>6898948</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3211,18 +3216,12 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3241,10 +3240,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133623458</v>
+        <v>133623446</v>
       </c>
       <c r="B28" t="n">
-        <v>91928</v>
+        <v>57958</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3252,37 +3251,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620239</v>
+        <v>620339</v>
       </c>
       <c r="R28" t="n">
-        <v>6898916</v>
+        <v>6898847</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3338,45 +3342,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133623426</v>
+        <v>133623463</v>
       </c>
       <c r="B29" t="n">
-        <v>91891</v>
+        <v>92659</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>757</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620174</v>
+        <v>620142</v>
       </c>
       <c r="R29" t="n">
-        <v>6898936</v>
+        <v>6898946</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3411,12 +3418,18 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3435,10 +3448,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133623402</v>
+        <v>133623458</v>
       </c>
       <c r="B30" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3446,45 +3459,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620109</v>
+        <v>620239</v>
       </c>
       <c r="R30" t="n">
-        <v>6898948</v>
+        <v>6898916</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3540,53 +3545,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133623446</v>
+        <v>133623426</v>
       </c>
       <c r="B31" t="n">
-        <v>57958</v>
+        <v>91891</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620339</v>
+        <v>620174</v>
       </c>
       <c r="R31" t="n">
-        <v>6898847</v>
+        <v>6898936</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -3135,10 +3135,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133623402</v>
+        <v>133623463</v>
       </c>
       <c r="B27" t="n">
-        <v>57958</v>
+        <v>92659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3146,31 +3146,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>757</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3178,13 +3173,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620109</v>
+        <v>620142</v>
       </c>
       <c r="R27" t="n">
-        <v>6898948</v>
+        <v>6898946</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3216,12 +3211,18 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3240,10 +3241,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133623446</v>
+        <v>133623458</v>
       </c>
       <c r="B28" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3251,42 +3252,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620339</v>
+        <v>620239</v>
       </c>
       <c r="R28" t="n">
-        <v>6898847</v>
+        <v>6898916</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3342,48 +3338,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133623463</v>
+        <v>133623426</v>
       </c>
       <c r="B29" t="n">
-        <v>92659</v>
+        <v>91891</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>757</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620142</v>
+        <v>620174</v>
       </c>
       <c r="R29" t="n">
-        <v>6898946</v>
+        <v>6898936</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3418,18 +3411,12 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3448,10 +3435,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133623458</v>
+        <v>133623402</v>
       </c>
       <c r="B30" t="n">
-        <v>91928</v>
+        <v>57958</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3459,37 +3446,45 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620239</v>
+        <v>620109</v>
       </c>
       <c r="R30" t="n">
-        <v>6898916</v>
+        <v>6898948</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3545,48 +3540,53 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133623426</v>
+        <v>133623446</v>
       </c>
       <c r="B31" t="n">
-        <v>91891</v>
+        <v>57958</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620174</v>
+        <v>620339</v>
       </c>
       <c r="R31" t="n">
-        <v>6898936</v>
+        <v>6898847</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133623409</v>
+        <v>133623429</v>
       </c>
       <c r="B13" t="n">
-        <v>79924</v>
+        <v>91928</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620161</v>
+        <v>620275</v>
       </c>
       <c r="R13" t="n">
-        <v>6898969</v>
+        <v>6898905</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133623429</v>
+        <v>133623409</v>
       </c>
       <c r="B14" t="n">
-        <v>91928</v>
+        <v>79924</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620275</v>
+        <v>620161</v>
       </c>
       <c r="R14" t="n">
-        <v>6898905</v>
+        <v>6898969</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -3135,10 +3135,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133623463</v>
+        <v>133623402</v>
       </c>
       <c r="B27" t="n">
-        <v>92659</v>
+        <v>57958</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3146,26 +3146,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>757</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3173,13 +3178,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620142</v>
+        <v>620109</v>
       </c>
       <c r="R27" t="n">
-        <v>6898946</v>
+        <v>6898948</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3211,18 +3216,12 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3241,10 +3240,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133623458</v>
+        <v>133623446</v>
       </c>
       <c r="B28" t="n">
-        <v>91928</v>
+        <v>57958</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3252,37 +3251,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620239</v>
+        <v>620339</v>
       </c>
       <c r="R28" t="n">
-        <v>6898916</v>
+        <v>6898847</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3338,45 +3342,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133623426</v>
+        <v>133623463</v>
       </c>
       <c r="B29" t="n">
-        <v>91891</v>
+        <v>92659</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>757</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620174</v>
+        <v>620142</v>
       </c>
       <c r="R29" t="n">
-        <v>6898936</v>
+        <v>6898946</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3411,12 +3418,18 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3435,10 +3448,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133623402</v>
+        <v>133623458</v>
       </c>
       <c r="B30" t="n">
-        <v>57958</v>
+        <v>91928</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3446,45 +3459,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620109</v>
+        <v>620239</v>
       </c>
       <c r="R30" t="n">
-        <v>6898948</v>
+        <v>6898916</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3540,53 +3545,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133623446</v>
+        <v>133623426</v>
       </c>
       <c r="B31" t="n">
-        <v>57958</v>
+        <v>91891</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620339</v>
+        <v>620174</v>
       </c>
       <c r="R31" t="n">
-        <v>6898847</v>
+        <v>6898936</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133623415</v>
+        <v>133623447</v>
       </c>
       <c r="B2" t="n">
-        <v>91891</v>
+        <v>79348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620235</v>
+        <v>620318</v>
       </c>
       <c r="R2" t="n">
-        <v>6898961</v>
+        <v>6898875</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133623413</v>
+        <v>133623460</v>
       </c>
       <c r="B3" t="n">
-        <v>79334</v>
+        <v>57965</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620178</v>
+        <v>620244</v>
       </c>
       <c r="R3" t="n">
-        <v>6898953</v>
+        <v>6898934</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -843,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133623447</v>
+        <v>133623415</v>
       </c>
       <c r="B4" t="n">
-        <v>79334</v>
+        <v>91910</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620318</v>
+        <v>620235</v>
       </c>
       <c r="R4" t="n">
-        <v>6898875</v>
+        <v>6898961</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133623460</v>
+        <v>133623413</v>
       </c>
       <c r="B5" t="n">
-        <v>57958</v>
+        <v>79348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,42 +987,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620244</v>
+        <v>620178</v>
       </c>
       <c r="R5" t="n">
-        <v>6898934</v>
+        <v>6898953</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1042,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,7 +1076,7 @@
         <v>133623430</v>
       </c>
       <c r="B6" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133623410</v>
+        <v>133623435</v>
       </c>
       <c r="B7" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620159</v>
+        <v>620315</v>
       </c>
       <c r="R7" t="n">
-        <v>6898960</v>
+        <v>6899013</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133623435</v>
+        <v>133623403</v>
       </c>
       <c r="B8" t="n">
-        <v>79366</v>
+        <v>79348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620315</v>
+        <v>620099</v>
       </c>
       <c r="R8" t="n">
-        <v>6899013</v>
+        <v>6898937</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133623403</v>
+        <v>133623455</v>
       </c>
       <c r="B9" t="n">
-        <v>79334</v>
+        <v>91910</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620099</v>
+        <v>620268</v>
       </c>
       <c r="R9" t="n">
-        <v>6898937</v>
+        <v>6898926</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133623455</v>
+        <v>133623410</v>
       </c>
       <c r="B10" t="n">
-        <v>91891</v>
+        <v>79380</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620268</v>
+        <v>620159</v>
       </c>
       <c r="R10" t="n">
-        <v>6898926</v>
+        <v>6898960</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1561,7 +1561,7 @@
         <v>133623407</v>
       </c>
       <c r="B11" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>133623440</v>
       </c>
       <c r="B12" t="n">
-        <v>5179</v>
+        <v>5181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133623429</v>
+        <v>133623409</v>
       </c>
       <c r="B13" t="n">
-        <v>91928</v>
+        <v>79938</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620275</v>
+        <v>620161</v>
       </c>
       <c r="R13" t="n">
-        <v>6898905</v>
+        <v>6898969</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133623409</v>
+        <v>133623429</v>
       </c>
       <c r="B14" t="n">
-        <v>79924</v>
+        <v>91947</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620161</v>
+        <v>620275</v>
       </c>
       <c r="R14" t="n">
-        <v>6898969</v>
+        <v>6898905</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1954,7 +1954,7 @@
         <v>133623436</v>
       </c>
       <c r="B15" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>133623434</v>
       </c>
       <c r="B16" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>133623431</v>
       </c>
       <c r="B17" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>133623442</v>
       </c>
       <c r="B18" t="n">
-        <v>4775</v>
+        <v>4776</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>133623411</v>
       </c>
       <c r="B19" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>133623465</v>
       </c>
       <c r="B20" t="n">
-        <v>79953</v>
+        <v>79967</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>133623443</v>
       </c>
       <c r="B21" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>133623423</v>
       </c>
       <c r="B22" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>133623448</v>
       </c>
       <c r="B23" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2844,32 +2844,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133623444</v>
+        <v>133623452</v>
       </c>
       <c r="B24" t="n">
-        <v>91928</v>
+        <v>91910</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620341</v>
+        <v>620384</v>
       </c>
       <c r="R24" t="n">
-        <v>6898817</v>
+        <v>6898898</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2941,32 +2941,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133623452</v>
+        <v>133623422</v>
       </c>
       <c r="B25" t="n">
-        <v>91891</v>
+        <v>80453</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620384</v>
+        <v>620275</v>
       </c>
       <c r="R25" t="n">
-        <v>6898898</v>
+        <v>6898953</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3038,10 +3038,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133623422</v>
+        <v>133623444</v>
       </c>
       <c r="B26" t="n">
-        <v>80439</v>
+        <v>91947</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3049,21 +3049,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620275</v>
+        <v>620341</v>
       </c>
       <c r="R26" t="n">
-        <v>6898953</v>
+        <v>6898817</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3135,10 +3135,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133623402</v>
+        <v>133623463</v>
       </c>
       <c r="B27" t="n">
-        <v>57958</v>
+        <v>92689</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3146,31 +3146,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>757</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3178,13 +3173,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620109</v>
+        <v>620142</v>
       </c>
       <c r="R27" t="n">
-        <v>6898948</v>
+        <v>6898946</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3216,12 +3211,18 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3240,10 +3241,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133623446</v>
+        <v>133623402</v>
       </c>
       <c r="B28" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3269,21 +3270,24 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620339</v>
+        <v>620109</v>
       </c>
       <c r="R28" t="n">
-        <v>6898847</v>
+        <v>6898948</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3342,10 +3346,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133623463</v>
+        <v>133623446</v>
       </c>
       <c r="B29" t="n">
-        <v>92659</v>
+        <v>57965</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3353,40 +3357,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>757</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620142</v>
+        <v>620339</v>
       </c>
       <c r="R29" t="n">
-        <v>6898946</v>
+        <v>6898847</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3418,18 +3424,12 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3448,32 +3448,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133623458</v>
+        <v>133623426</v>
       </c>
       <c r="B30" t="n">
-        <v>91928</v>
+        <v>91910</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3483,10 +3483,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620239</v>
+        <v>620174</v>
       </c>
       <c r="R30" t="n">
-        <v>6898916</v>
+        <v>6898936</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3545,32 +3545,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133623426</v>
+        <v>133623458</v>
       </c>
       <c r="B31" t="n">
-        <v>91891</v>
+        <v>91947</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620174</v>
+        <v>620239</v>
       </c>
       <c r="R31" t="n">
-        <v>6898936</v>
+        <v>6898916</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3645,7 +3645,7 @@
         <v>133623462</v>
       </c>
       <c r="B32" t="n">
-        <v>92659</v>
+        <v>92689</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3744,10 +3744,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133623438</v>
+        <v>133623433</v>
       </c>
       <c r="B33" t="n">
-        <v>79000</v>
+        <v>83325</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3755,21 +3755,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3779,10 +3779,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620335</v>
+        <v>620290</v>
       </c>
       <c r="R33" t="n">
-        <v>6898933</v>
+        <v>6898929</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3841,32 +3841,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133623433</v>
+        <v>133623464</v>
       </c>
       <c r="B34" t="n">
-        <v>83311</v>
+        <v>91910</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3876,10 +3876,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>620290</v>
+        <v>620127</v>
       </c>
       <c r="R34" t="n">
-        <v>6898929</v>
+        <v>6898927</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3941,7 +3941,7 @@
         <v>133623459</v>
       </c>
       <c r="B35" t="n">
-        <v>81319</v>
+        <v>81333</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4035,32 +4035,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133623464</v>
+        <v>133623438</v>
       </c>
       <c r="B36" t="n">
-        <v>91891</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620127</v>
+        <v>620335</v>
       </c>
       <c r="R36" t="n">
-        <v>6898927</v>
+        <v>6898933</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4132,32 +4132,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133623421</v>
+        <v>133623432</v>
       </c>
       <c r="B37" t="n">
-        <v>79366</v>
+        <v>91910</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620249</v>
+        <v>620266</v>
       </c>
       <c r="R37" t="n">
-        <v>6898992</v>
+        <v>6898927</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4229,32 +4229,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133623432</v>
+        <v>133623421</v>
       </c>
       <c r="B38" t="n">
-        <v>91891</v>
+        <v>79380</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4264,10 +4264,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>620266</v>
+        <v>620249</v>
       </c>
       <c r="R38" t="n">
-        <v>6898927</v>
+        <v>6898992</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4329,7 +4329,7 @@
         <v>133623437</v>
       </c>
       <c r="B39" t="n">
-        <v>79953</v>
+        <v>79967</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>133623408</v>
       </c>
       <c r="B40" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>133623428</v>
       </c>
       <c r="B41" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>133623404</v>
       </c>
       <c r="B42" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>133623424</v>
       </c>
       <c r="B43" t="n">
-        <v>79953</v>
+        <v>79967</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4816,10 +4816,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133623439</v>
+        <v>133623412</v>
       </c>
       <c r="B44" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>620336</v>
+        <v>620162</v>
       </c>
       <c r="R44" t="n">
-        <v>6898875</v>
+        <v>6899008</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4913,10 +4913,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133623412</v>
+        <v>133623439</v>
       </c>
       <c r="B45" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4948,10 +4948,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>620162</v>
+        <v>620336</v>
       </c>
       <c r="R45" t="n">
-        <v>6899008</v>
+        <v>6898875</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5013,7 +5013,7 @@
         <v>133623425</v>
       </c>
       <c r="B46" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>133623445</v>
       </c>
       <c r="B47" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>133623453</v>
       </c>
       <c r="B48" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>133623417</v>
       </c>
       <c r="B49" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5398,10 +5398,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133623456</v>
+        <v>133623466</v>
       </c>
       <c r="B50" t="n">
-        <v>91928</v>
+        <v>91968</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5409,21 +5409,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5433,10 +5433,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>620264</v>
+        <v>620116</v>
       </c>
       <c r="R50" t="n">
-        <v>6898924</v>
+        <v>6898986</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5495,10 +5495,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133623466</v>
+        <v>133623456</v>
       </c>
       <c r="B51" t="n">
-        <v>91949</v>
+        <v>91947</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5506,21 +5506,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>620116</v>
+        <v>620264</v>
       </c>
       <c r="R51" t="n">
-        <v>6898986</v>
+        <v>6898924</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5595,7 +5595,7 @@
         <v>133815458</v>
       </c>
       <c r="B52" t="n">
-        <v>58119</v>
+        <v>58126</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133623447</v>
+        <v>133623413</v>
       </c>
       <c r="B2" t="n">
         <v>79348</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620318</v>
+        <v>620178</v>
       </c>
       <c r="R2" t="n">
-        <v>6898875</v>
+        <v>6898953</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,53 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133623460</v>
+        <v>133623415</v>
       </c>
       <c r="B3" t="n">
-        <v>57965</v>
+        <v>91910</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620244</v>
+        <v>620235</v>
       </c>
       <c r="R3" t="n">
-        <v>6898934</v>
+        <v>6898961</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -848,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133623415</v>
+        <v>133623447</v>
       </c>
       <c r="B4" t="n">
-        <v>91910</v>
+        <v>79348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620235</v>
+        <v>620318</v>
       </c>
       <c r="R4" t="n">
-        <v>6898961</v>
+        <v>6898875</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -976,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133623413</v>
+        <v>133623460</v>
       </c>
       <c r="B5" t="n">
-        <v>79348</v>
+        <v>57965</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,37 +977,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620178</v>
+        <v>620244</v>
       </c>
       <c r="R5" t="n">
-        <v>6898953</v>
+        <v>6898934</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1047,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133623435</v>
+        <v>133623455</v>
       </c>
       <c r="B7" t="n">
-        <v>79380</v>
+        <v>91910</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620315</v>
+        <v>620268</v>
       </c>
       <c r="R7" t="n">
-        <v>6899013</v>
+        <v>6898926</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133623403</v>
+        <v>133623435</v>
       </c>
       <c r="B8" t="n">
-        <v>79348</v>
+        <v>79380</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620099</v>
+        <v>620315</v>
       </c>
       <c r="R8" t="n">
-        <v>6898937</v>
+        <v>6899013</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133623455</v>
+        <v>133623403</v>
       </c>
       <c r="B9" t="n">
-        <v>91910</v>
+        <v>79348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620268</v>
+        <v>620099</v>
       </c>
       <c r="R9" t="n">
-        <v>6898926</v>
+        <v>6898937</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -2145,45 +2145,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133623431</v>
+        <v>133623442</v>
       </c>
       <c r="B17" t="n">
-        <v>79348</v>
+        <v>4776</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620266</v>
+        <v>620347</v>
       </c>
       <c r="R17" t="n">
-        <v>6898928</v>
+        <v>6898852</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2224,6 +2233,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2242,54 +2252,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133623442</v>
+        <v>133623411</v>
       </c>
       <c r="B18" t="n">
-        <v>4776</v>
+        <v>79380</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100299</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620347</v>
+        <v>620166</v>
       </c>
       <c r="R18" t="n">
-        <v>6898852</v>
+        <v>6898962</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2330,7 +2331,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2349,10 +2349,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133623411</v>
+        <v>133623431</v>
       </c>
       <c r="B19" t="n">
-        <v>79380</v>
+        <v>79348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2360,21 +2360,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620166</v>
+        <v>620266</v>
       </c>
       <c r="R19" t="n">
-        <v>6898962</v>
+        <v>6898928</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2446,10 +2446,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133623465</v>
+        <v>133623448</v>
       </c>
       <c r="B20" t="n">
-        <v>79967</v>
+        <v>57965</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2457,37 +2457,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620113</v>
+        <v>620324</v>
       </c>
       <c r="R20" t="n">
-        <v>6898932</v>
+        <v>6898861</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2517,6 +2522,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2640,10 +2650,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133623423</v>
+        <v>133623465</v>
       </c>
       <c r="B22" t="n">
-        <v>79348</v>
+        <v>79967</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,21 +2661,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2675,10 +2685,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620235</v>
+        <v>620113</v>
       </c>
       <c r="R22" t="n">
-        <v>6898952</v>
+        <v>6898932</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2737,10 +2747,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133623448</v>
+        <v>133623423</v>
       </c>
       <c r="B23" t="n">
-        <v>57965</v>
+        <v>79348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,42 +2758,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620324</v>
+        <v>620235</v>
       </c>
       <c r="R23" t="n">
-        <v>6898861</v>
+        <v>6898952</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2813,11 +2818,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2844,32 +2844,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133623452</v>
+        <v>133623422</v>
       </c>
       <c r="B24" t="n">
-        <v>91910</v>
+        <v>80453</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620384</v>
+        <v>620275</v>
       </c>
       <c r="R24" t="n">
-        <v>6898898</v>
+        <v>6898953</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133623422</v>
+        <v>133623444</v>
       </c>
       <c r="B25" t="n">
-        <v>80453</v>
+        <v>91947</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2952,21 +2952,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620275</v>
+        <v>620341</v>
       </c>
       <c r="R25" t="n">
-        <v>6898953</v>
+        <v>6898817</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3038,32 +3038,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133623444</v>
+        <v>133623452</v>
       </c>
       <c r="B26" t="n">
-        <v>91947</v>
+        <v>91910</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620341</v>
+        <v>620384</v>
       </c>
       <c r="R26" t="n">
-        <v>6898817</v>
+        <v>6898898</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3135,10 +3135,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133623463</v>
+        <v>133623402</v>
       </c>
       <c r="B27" t="n">
-        <v>92689</v>
+        <v>57965</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3146,26 +3146,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>757</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3173,13 +3178,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620142</v>
+        <v>620109</v>
       </c>
       <c r="R27" t="n">
-        <v>6898946</v>
+        <v>6898948</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3211,18 +3216,12 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3241,7 +3240,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133623402</v>
+        <v>133623446</v>
       </c>
       <c r="B28" t="n">
         <v>57965</v>
@@ -3270,24 +3269,21 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620109</v>
+        <v>620339</v>
       </c>
       <c r="R28" t="n">
-        <v>6898948</v>
+        <v>6898847</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3346,10 +3342,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133623446</v>
+        <v>133623463</v>
       </c>
       <c r="B29" t="n">
-        <v>57965</v>
+        <v>92689</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3357,42 +3353,40 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>757</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620339</v>
+        <v>620142</v>
       </c>
       <c r="R29" t="n">
-        <v>6898847</v>
+        <v>6898946</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3424,12 +3418,18 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133623462</v>
+        <v>133623433</v>
       </c>
       <c r="B32" t="n">
-        <v>92689</v>
+        <v>83325</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3653,21 +3653,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>757</v>
+        <v>308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620130</v>
+        <v>620290</v>
       </c>
       <c r="R32" t="n">
-        <v>6898930</v>
+        <v>6898929</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3713,11 +3713,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar. Röd KOH-reaktion</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3744,32 +3739,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133623433</v>
+        <v>133623464</v>
       </c>
       <c r="B33" t="n">
-        <v>83325</v>
+        <v>91910</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3779,10 +3774,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620290</v>
+        <v>620127</v>
       </c>
       <c r="R33" t="n">
-        <v>6898929</v>
+        <v>6898927</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3841,32 +3836,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133623464</v>
+        <v>133623462</v>
       </c>
       <c r="B34" t="n">
-        <v>91910</v>
+        <v>92689</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>757</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3876,10 +3871,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>620127</v>
+        <v>620130</v>
       </c>
       <c r="R34" t="n">
-        <v>6898927</v>
+        <v>6898930</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3912,6 +3907,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar. Röd KOH-reaktion</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3941,7 +3941,7 @@
         <v>133623459</v>
       </c>
       <c r="B35" t="n">
-        <v>81333</v>
+        <v>81330</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4132,32 +4132,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133623432</v>
+        <v>133623421</v>
       </c>
       <c r="B37" t="n">
-        <v>91910</v>
+        <v>79380</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620266</v>
+        <v>620249</v>
       </c>
       <c r="R37" t="n">
-        <v>6898927</v>
+        <v>6898992</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4229,32 +4229,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133623421</v>
+        <v>133623432</v>
       </c>
       <c r="B38" t="n">
-        <v>79380</v>
+        <v>91910</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4264,10 +4264,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>620249</v>
+        <v>620266</v>
       </c>
       <c r="R38" t="n">
-        <v>6898992</v>
+        <v>6898927</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4326,10 +4326,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133623437</v>
+        <v>133623408</v>
       </c>
       <c r="B39" t="n">
-        <v>79967</v>
+        <v>57965</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4337,37 +4337,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>620340</v>
+        <v>620156</v>
       </c>
       <c r="R39" t="n">
-        <v>6898950</v>
+        <v>6898981</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4423,10 +4428,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133623408</v>
+        <v>133623437</v>
       </c>
       <c r="B40" t="n">
-        <v>57965</v>
+        <v>79967</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4434,42 +4439,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>620156</v>
+        <v>620340</v>
       </c>
       <c r="R40" t="n">
-        <v>6898981</v>
+        <v>6898950</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133623412</v>
+        <v>133623439</v>
       </c>
       <c r="B44" t="n">
         <v>79380</v>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>620162</v>
+        <v>620336</v>
       </c>
       <c r="R44" t="n">
-        <v>6899008</v>
+        <v>6898875</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4913,7 +4913,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133623439</v>
+        <v>133623412</v>
       </c>
       <c r="B45" t="n">
         <v>79380</v>
@@ -4948,10 +4948,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>620336</v>
+        <v>620162</v>
       </c>
       <c r="R45" t="n">
-        <v>6898875</v>
+        <v>6899008</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5010,10 +5010,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133623425</v>
+        <v>133623453</v>
       </c>
       <c r="B46" t="n">
-        <v>91947</v>
+        <v>79348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5021,21 +5021,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>620196</v>
+        <v>620262</v>
       </c>
       <c r="R46" t="n">
-        <v>6898959</v>
+        <v>6898935</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5107,7 +5107,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133623445</v>
+        <v>133623425</v>
       </c>
       <c r="B47" t="n">
         <v>91947</v>
@@ -5142,10 +5142,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>620349</v>
+        <v>620196</v>
       </c>
       <c r="R47" t="n">
-        <v>6898830</v>
+        <v>6898959</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5204,10 +5204,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133623453</v>
+        <v>133623445</v>
       </c>
       <c r="B48" t="n">
-        <v>79348</v>
+        <v>91947</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5215,21 +5215,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620262</v>
+        <v>620349</v>
       </c>
       <c r="R48" t="n">
-        <v>6898935</v>
+        <v>6898830</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133623413</v>
+        <v>133623415</v>
       </c>
       <c r="B2" t="n">
-        <v>79348</v>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620178</v>
+        <v>620235</v>
       </c>
       <c r="R2" t="n">
-        <v>6898953</v>
+        <v>6898961</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133623415</v>
+        <v>133623413</v>
       </c>
       <c r="B3" t="n">
-        <v>91910</v>
+        <v>79358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620235</v>
+        <v>620178</v>
       </c>
       <c r="R3" t="n">
-        <v>6898961</v>
+        <v>6898953</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,7 +872,7 @@
         <v>133623447</v>
       </c>
       <c r="B4" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>133623460</v>
       </c>
       <c r="B5" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133623430</v>
+        <v>133623435</v>
       </c>
       <c r="B6" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620267</v>
+        <v>620315</v>
       </c>
       <c r="R6" t="n">
-        <v>6898931</v>
+        <v>6899013</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133623455</v>
+        <v>133623403</v>
       </c>
       <c r="B7" t="n">
-        <v>91910</v>
+        <v>79358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620268</v>
+        <v>620099</v>
       </c>
       <c r="R7" t="n">
-        <v>6898926</v>
+        <v>6898937</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133623435</v>
+        <v>133623430</v>
       </c>
       <c r="B8" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620315</v>
+        <v>620267</v>
       </c>
       <c r="R8" t="n">
-        <v>6899013</v>
+        <v>6898931</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133623403</v>
+        <v>133623410</v>
       </c>
       <c r="B9" t="n">
-        <v>79348</v>
+        <v>79390</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620099</v>
+        <v>620159</v>
       </c>
       <c r="R9" t="n">
-        <v>6898937</v>
+        <v>6898960</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133623410</v>
+        <v>133623455</v>
       </c>
       <c r="B10" t="n">
-        <v>79380</v>
+        <v>91920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620159</v>
+        <v>620268</v>
       </c>
       <c r="R10" t="n">
-        <v>6898960</v>
+        <v>6898926</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1561,7 +1561,7 @@
         <v>133623407</v>
       </c>
       <c r="B11" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>133623409</v>
       </c>
       <c r="B13" t="n">
-        <v>79938</v>
+        <v>79948</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>133623429</v>
       </c>
       <c r="B14" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>133623436</v>
       </c>
       <c r="B15" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>133623434</v>
       </c>
       <c r="B16" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2145,54 +2145,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133623442</v>
+        <v>133623431</v>
       </c>
       <c r="B17" t="n">
-        <v>4776</v>
+        <v>79358</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620347</v>
+        <v>620266</v>
       </c>
       <c r="R17" t="n">
-        <v>6898852</v>
+        <v>6898928</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2233,7 +2224,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2252,45 +2242,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133623411</v>
+        <v>133623442</v>
       </c>
       <c r="B18" t="n">
-        <v>79380</v>
+        <v>4776</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>100299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620166</v>
+        <v>620347</v>
       </c>
       <c r="R18" t="n">
-        <v>6898962</v>
+        <v>6898852</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2331,6 +2330,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2349,10 +2349,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133623431</v>
+        <v>133623411</v>
       </c>
       <c r="B19" t="n">
-        <v>79348</v>
+        <v>79390</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2360,21 +2360,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620266</v>
+        <v>620166</v>
       </c>
       <c r="R19" t="n">
-        <v>6898928</v>
+        <v>6898962</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2446,10 +2446,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133623448</v>
+        <v>133623465</v>
       </c>
       <c r="B20" t="n">
-        <v>57965</v>
+        <v>79977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2457,42 +2457,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620324</v>
+        <v>620113</v>
       </c>
       <c r="R20" t="n">
-        <v>6898861</v>
+        <v>6898932</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2522,11 +2517,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2556,7 +2546,7 @@
         <v>133623443</v>
       </c>
       <c r="B21" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2650,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133623465</v>
+        <v>133623423</v>
       </c>
       <c r="B22" t="n">
-        <v>79967</v>
+        <v>79358</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2661,21 +2651,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2685,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620113</v>
+        <v>620235</v>
       </c>
       <c r="R22" t="n">
-        <v>6898932</v>
+        <v>6898952</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2747,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133623423</v>
+        <v>133623448</v>
       </c>
       <c r="B23" t="n">
-        <v>79348</v>
+        <v>57975</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2758,37 +2748,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620235</v>
+        <v>620324</v>
       </c>
       <c r="R23" t="n">
-        <v>6898952</v>
+        <v>6898861</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2818,6 +2813,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2844,32 +2844,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133623422</v>
+        <v>133623452</v>
       </c>
       <c r="B24" t="n">
-        <v>80453</v>
+        <v>91920</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620275</v>
+        <v>620384</v>
       </c>
       <c r="R24" t="n">
-        <v>6898953</v>
+        <v>6898898</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133623444</v>
+        <v>133623422</v>
       </c>
       <c r="B25" t="n">
-        <v>91947</v>
+        <v>80473</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2952,21 +2952,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620341</v>
+        <v>620275</v>
       </c>
       <c r="R25" t="n">
-        <v>6898817</v>
+        <v>6898953</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3038,32 +3038,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133623452</v>
+        <v>133623444</v>
       </c>
       <c r="B26" t="n">
-        <v>91910</v>
+        <v>91957</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620384</v>
+        <v>620341</v>
       </c>
       <c r="R26" t="n">
-        <v>6898898</v>
+        <v>6898817</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3138,7 +3138,7 @@
         <v>133623402</v>
       </c>
       <c r="B27" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>133623446</v>
       </c>
       <c r="B28" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3342,48 +3342,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133623463</v>
+        <v>133623426</v>
       </c>
       <c r="B29" t="n">
-        <v>92689</v>
+        <v>91920</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>757</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620142</v>
+        <v>620174</v>
       </c>
       <c r="R29" t="n">
-        <v>6898946</v>
+        <v>6898936</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3418,18 +3415,12 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3448,32 +3439,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133623426</v>
+        <v>133623458</v>
       </c>
       <c r="B30" t="n">
-        <v>91910</v>
+        <v>91957</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3483,10 +3474,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620174</v>
+        <v>620239</v>
       </c>
       <c r="R30" t="n">
-        <v>6898936</v>
+        <v>6898916</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3545,10 +3536,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133623458</v>
+        <v>133623463</v>
       </c>
       <c r="B31" t="n">
-        <v>91947</v>
+        <v>92699</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3556,34 +3547,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>757</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620239</v>
+        <v>620142</v>
       </c>
       <c r="R31" t="n">
-        <v>6898916</v>
+        <v>6898946</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3618,12 +3612,18 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133623433</v>
+        <v>133623462</v>
       </c>
       <c r="B32" t="n">
-        <v>83325</v>
+        <v>92699</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3653,21 +3653,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>757</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620290</v>
+        <v>620130</v>
       </c>
       <c r="R32" t="n">
-        <v>6898929</v>
+        <v>6898930</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3713,6 +3713,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar. Röd KOH-reaktion</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3739,32 +3744,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133623464</v>
+        <v>133623433</v>
       </c>
       <c r="B33" t="n">
-        <v>91910</v>
+        <v>83335</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3774,10 +3779,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620127</v>
+        <v>620290</v>
       </c>
       <c r="R33" t="n">
-        <v>6898927</v>
+        <v>6898929</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3836,10 +3841,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133623462</v>
+        <v>133623438</v>
       </c>
       <c r="B34" t="n">
-        <v>92689</v>
+        <v>79024</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3847,21 +3852,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>757</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3871,10 +3876,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>620130</v>
+        <v>620335</v>
       </c>
       <c r="R34" t="n">
-        <v>6898930</v>
+        <v>6898933</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3907,11 +3912,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar. Röd KOH-reaktion</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3938,32 +3938,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133623459</v>
+        <v>133623464</v>
       </c>
       <c r="B35" t="n">
-        <v>81330</v>
+        <v>91920</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1049</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3973,10 +3973,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>620266</v>
+        <v>620127</v>
       </c>
       <c r="R35" t="n">
-        <v>6898988</v>
+        <v>6898927</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4035,10 +4035,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133623438</v>
+        <v>133623459</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>81340</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4046,21 +4046,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620335</v>
+        <v>620266</v>
       </c>
       <c r="R36" t="n">
-        <v>6898933</v>
+        <v>6898988</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4132,32 +4132,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133623421</v>
+        <v>133623432</v>
       </c>
       <c r="B37" t="n">
-        <v>79380</v>
+        <v>91920</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620249</v>
+        <v>620266</v>
       </c>
       <c r="R37" t="n">
-        <v>6898992</v>
+        <v>6898927</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4229,32 +4229,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133623432</v>
+        <v>133623421</v>
       </c>
       <c r="B38" t="n">
-        <v>91910</v>
+        <v>79390</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4264,10 +4264,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>620266</v>
+        <v>620249</v>
       </c>
       <c r="R38" t="n">
-        <v>6898927</v>
+        <v>6898992</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4326,10 +4326,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133623408</v>
+        <v>133623437</v>
       </c>
       <c r="B39" t="n">
-        <v>57965</v>
+        <v>79977</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4337,42 +4337,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>620156</v>
+        <v>620340</v>
       </c>
       <c r="R39" t="n">
-        <v>6898981</v>
+        <v>6898950</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4428,10 +4423,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133623437</v>
+        <v>133623408</v>
       </c>
       <c r="B40" t="n">
-        <v>79967</v>
+        <v>57975</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4439,37 +4434,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>620340</v>
+        <v>620156</v>
       </c>
       <c r="R40" t="n">
-        <v>6898950</v>
+        <v>6898981</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4525,10 +4525,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133623428</v>
+        <v>133623404</v>
       </c>
       <c r="B41" t="n">
-        <v>91947</v>
+        <v>79390</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4536,21 +4536,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>620196</v>
+        <v>620098</v>
       </c>
       <c r="R41" t="n">
-        <v>6898931</v>
+        <v>6898939</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4622,10 +4622,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133623404</v>
+        <v>133623428</v>
       </c>
       <c r="B42" t="n">
-        <v>79380</v>
+        <v>91957</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4633,21 +4633,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4657,10 +4657,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620098</v>
+        <v>620196</v>
       </c>
       <c r="R42" t="n">
-        <v>6898939</v>
+        <v>6898931</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4722,7 +4722,7 @@
         <v>133623424</v>
       </c>
       <c r="B43" t="n">
-        <v>79967</v>
+        <v>79977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4816,10 +4816,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133623439</v>
+        <v>133623412</v>
       </c>
       <c r="B44" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>620336</v>
+        <v>620162</v>
       </c>
       <c r="R44" t="n">
-        <v>6898875</v>
+        <v>6899008</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4913,10 +4913,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133623412</v>
+        <v>133623439</v>
       </c>
       <c r="B45" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4948,10 +4948,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>620162</v>
+        <v>620336</v>
       </c>
       <c r="R45" t="n">
-        <v>6899008</v>
+        <v>6898875</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5010,10 +5010,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133623453</v>
+        <v>133623425</v>
       </c>
       <c r="B46" t="n">
-        <v>79348</v>
+        <v>91957</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5021,21 +5021,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>620262</v>
+        <v>620196</v>
       </c>
       <c r="R46" t="n">
-        <v>6898935</v>
+        <v>6898959</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5107,10 +5107,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133623425</v>
+        <v>133623445</v>
       </c>
       <c r="B47" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5142,10 +5142,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>620196</v>
+        <v>620349</v>
       </c>
       <c r="R47" t="n">
-        <v>6898959</v>
+        <v>6898830</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5204,10 +5204,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133623445</v>
+        <v>133623453</v>
       </c>
       <c r="B48" t="n">
-        <v>91947</v>
+        <v>79358</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5215,21 +5215,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620349</v>
+        <v>620262</v>
       </c>
       <c r="R48" t="n">
-        <v>6898830</v>
+        <v>6898935</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5304,7 +5304,7 @@
         <v>133623417</v>
       </c>
       <c r="B49" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>133623466</v>
       </c>
       <c r="B50" t="n">
-        <v>91968</v>
+        <v>91978</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>133623456</v>
       </c>
       <c r="B51" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>133815458</v>
       </c>
       <c r="B52" t="n">
-        <v>58126</v>
+        <v>58136</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133623413</v>
+        <v>133623447</v>
       </c>
       <c r="B3" t="n">
         <v>79358</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620178</v>
+        <v>620318</v>
       </c>
       <c r="R3" t="n">
-        <v>6898953</v>
+        <v>6898875</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133623447</v>
+        <v>133623460</v>
       </c>
       <c r="B4" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,37 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620318</v>
+        <v>620244</v>
       </c>
       <c r="R4" t="n">
-        <v>6898875</v>
+        <v>6898934</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -940,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133623460</v>
+        <v>133623413</v>
       </c>
       <c r="B5" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,42 +987,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620244</v>
+        <v>620178</v>
       </c>
       <c r="R5" t="n">
-        <v>6898934</v>
+        <v>6898953</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1042,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133623403</v>
+        <v>133623430</v>
       </c>
       <c r="B7" t="n">
-        <v>79358</v>
+        <v>79390</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620099</v>
+        <v>620267</v>
       </c>
       <c r="R7" t="n">
-        <v>6898937</v>
+        <v>6898931</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133623430</v>
+        <v>133623455</v>
       </c>
       <c r="B8" t="n">
-        <v>79390</v>
+        <v>91920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620267</v>
+        <v>620268</v>
       </c>
       <c r="R8" t="n">
-        <v>6898931</v>
+        <v>6898926</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133623455</v>
+        <v>133623403</v>
       </c>
       <c r="B10" t="n">
-        <v>91920</v>
+        <v>79358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620268</v>
+        <v>620099</v>
       </c>
       <c r="R10" t="n">
-        <v>6898926</v>
+        <v>6898937</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133623431</v>
+        <v>133623411</v>
       </c>
       <c r="B17" t="n">
-        <v>79358</v>
+        <v>79390</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620266</v>
+        <v>620166</v>
       </c>
       <c r="R17" t="n">
-        <v>6898928</v>
+        <v>6898962</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2349,10 +2349,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133623411</v>
+        <v>133623431</v>
       </c>
       <c r="B19" t="n">
-        <v>79390</v>
+        <v>79358</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2360,21 +2360,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620166</v>
+        <v>620266</v>
       </c>
       <c r="R19" t="n">
-        <v>6898962</v>
+        <v>6898928</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2446,10 +2446,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133623465</v>
+        <v>133623443</v>
       </c>
       <c r="B20" t="n">
-        <v>79977</v>
+        <v>79358</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2457,21 +2457,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620113</v>
+        <v>620349</v>
       </c>
       <c r="R20" t="n">
-        <v>6898932</v>
+        <v>6898850</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2543,10 +2543,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133623443</v>
+        <v>133623465</v>
       </c>
       <c r="B21" t="n">
-        <v>79358</v>
+        <v>79977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2554,21 +2554,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620349</v>
+        <v>620113</v>
       </c>
       <c r="R21" t="n">
-        <v>6898850</v>
+        <v>6898932</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2844,32 +2844,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133623452</v>
+        <v>133623422</v>
       </c>
       <c r="B24" t="n">
-        <v>91920</v>
+        <v>80473</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620384</v>
+        <v>620275</v>
       </c>
       <c r="R24" t="n">
-        <v>6898898</v>
+        <v>6898953</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133623422</v>
+        <v>133623444</v>
       </c>
       <c r="B25" t="n">
-        <v>80473</v>
+        <v>91957</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2952,21 +2952,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620275</v>
+        <v>620341</v>
       </c>
       <c r="R25" t="n">
-        <v>6898953</v>
+        <v>6898817</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3038,32 +3038,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133623444</v>
+        <v>133623452</v>
       </c>
       <c r="B26" t="n">
-        <v>91957</v>
+        <v>91920</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620341</v>
+        <v>620384</v>
       </c>
       <c r="R26" t="n">
-        <v>6898817</v>
+        <v>6898898</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4132,32 +4132,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133623432</v>
+        <v>133623421</v>
       </c>
       <c r="B37" t="n">
-        <v>91920</v>
+        <v>79390</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620266</v>
+        <v>620249</v>
       </c>
       <c r="R37" t="n">
-        <v>6898927</v>
+        <v>6898992</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4229,32 +4229,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133623421</v>
+        <v>133623432</v>
       </c>
       <c r="B38" t="n">
-        <v>79390</v>
+        <v>91920</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4264,10 +4264,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>620249</v>
+        <v>620266</v>
       </c>
       <c r="R38" t="n">
-        <v>6898992</v>
+        <v>6898927</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5010,10 +5010,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133623425</v>
+        <v>133623453</v>
       </c>
       <c r="B46" t="n">
-        <v>91957</v>
+        <v>79358</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5021,21 +5021,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>620196</v>
+        <v>620262</v>
       </c>
       <c r="R46" t="n">
-        <v>6898959</v>
+        <v>6898935</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5204,10 +5204,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133623453</v>
+        <v>133623417</v>
       </c>
       <c r="B48" t="n">
-        <v>79358</v>
+        <v>80473</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5215,21 +5215,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620262</v>
+        <v>620220</v>
       </c>
       <c r="R48" t="n">
-        <v>6898935</v>
+        <v>6898975</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5301,10 +5301,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133623417</v>
+        <v>133623425</v>
       </c>
       <c r="B49" t="n">
-        <v>80473</v>
+        <v>91957</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5312,21 +5312,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>620220</v>
+        <v>620196</v>
       </c>
       <c r="R49" t="n">
-        <v>6898975</v>
+        <v>6898959</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -1073,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133623435</v>
+        <v>133623410</v>
       </c>
       <c r="B6" t="n">
         <v>79390</v>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620315</v>
+        <v>620159</v>
       </c>
       <c r="R6" t="n">
-        <v>6899013</v>
+        <v>6898960</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133623430</v>
+        <v>133623403</v>
       </c>
       <c r="B7" t="n">
-        <v>79390</v>
+        <v>79358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620267</v>
+        <v>620099</v>
       </c>
       <c r="R7" t="n">
-        <v>6898931</v>
+        <v>6898937</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133623455</v>
+        <v>133623435</v>
       </c>
       <c r="B8" t="n">
-        <v>91920</v>
+        <v>79390</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620268</v>
+        <v>620315</v>
       </c>
       <c r="R8" t="n">
-        <v>6898926</v>
+        <v>6899013</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133623410</v>
+        <v>133623430</v>
       </c>
       <c r="B9" t="n">
         <v>79390</v>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620159</v>
+        <v>620267</v>
       </c>
       <c r="R9" t="n">
-        <v>6898960</v>
+        <v>6898931</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133623403</v>
+        <v>133623455</v>
       </c>
       <c r="B10" t="n">
-        <v>79358</v>
+        <v>91920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620099</v>
+        <v>620268</v>
       </c>
       <c r="R10" t="n">
-        <v>6898937</v>
+        <v>6898926</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -2844,32 +2844,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133623422</v>
+        <v>133623452</v>
       </c>
       <c r="B24" t="n">
-        <v>80473</v>
+        <v>91920</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620275</v>
+        <v>620384</v>
       </c>
       <c r="R24" t="n">
-        <v>6898953</v>
+        <v>6898898</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133623444</v>
+        <v>133623422</v>
       </c>
       <c r="B25" t="n">
-        <v>91957</v>
+        <v>80473</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2952,21 +2952,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620341</v>
+        <v>620275</v>
       </c>
       <c r="R25" t="n">
-        <v>6898817</v>
+        <v>6898953</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3038,32 +3038,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133623452</v>
+        <v>133623444</v>
       </c>
       <c r="B26" t="n">
-        <v>91920</v>
+        <v>91957</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620384</v>
+        <v>620341</v>
       </c>
       <c r="R26" t="n">
-        <v>6898898</v>
+        <v>6898817</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133623462</v>
+        <v>133623459</v>
       </c>
       <c r="B32" t="n">
-        <v>92699</v>
+        <v>81340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3653,21 +3653,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>757</v>
+        <v>1049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620130</v>
+        <v>620266</v>
       </c>
       <c r="R32" t="n">
-        <v>6898930</v>
+        <v>6898988</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3713,11 +3713,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar. Röd KOH-reaktion</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3744,10 +3739,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133623433</v>
+        <v>133623462</v>
       </c>
       <c r="B33" t="n">
-        <v>83335</v>
+        <v>92699</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3755,21 +3750,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>757</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3779,10 +3774,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620290</v>
+        <v>620130</v>
       </c>
       <c r="R33" t="n">
-        <v>6898929</v>
+        <v>6898930</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3815,6 +3810,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar. Röd KOH-reaktion</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3841,10 +3841,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133623438</v>
+        <v>133623433</v>
       </c>
       <c r="B34" t="n">
-        <v>79024</v>
+        <v>83335</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3852,21 +3852,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3876,10 +3876,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>620335</v>
+        <v>620290</v>
       </c>
       <c r="R34" t="n">
-        <v>6898933</v>
+        <v>6898929</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3938,32 +3938,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133623464</v>
+        <v>133623438</v>
       </c>
       <c r="B35" t="n">
-        <v>91920</v>
+        <v>79024</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3973,10 +3973,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>620127</v>
+        <v>620335</v>
       </c>
       <c r="R35" t="n">
-        <v>6898927</v>
+        <v>6898933</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4035,32 +4035,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133623459</v>
+        <v>133623464</v>
       </c>
       <c r="B36" t="n">
-        <v>81340</v>
+        <v>91920</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1049</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620266</v>
+        <v>620127</v>
       </c>
       <c r="R36" t="n">
-        <v>6898988</v>
+        <v>6898927</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -1073,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133623410</v>
+        <v>133623435</v>
       </c>
       <c r="B6" t="n">
         <v>79390</v>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620159</v>
+        <v>620315</v>
       </c>
       <c r="R6" t="n">
-        <v>6898960</v>
+        <v>6899013</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133623403</v>
+        <v>133623430</v>
       </c>
       <c r="B7" t="n">
-        <v>79358</v>
+        <v>79390</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620099</v>
+        <v>620267</v>
       </c>
       <c r="R7" t="n">
-        <v>6898937</v>
+        <v>6898931</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133623435</v>
+        <v>133623455</v>
       </c>
       <c r="B8" t="n">
-        <v>79390</v>
+        <v>91920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620315</v>
+        <v>620268</v>
       </c>
       <c r="R8" t="n">
-        <v>6899013</v>
+        <v>6898926</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133623430</v>
+        <v>133623410</v>
       </c>
       <c r="B9" t="n">
         <v>79390</v>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620267</v>
+        <v>620159</v>
       </c>
       <c r="R9" t="n">
-        <v>6898931</v>
+        <v>6898960</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133623455</v>
+        <v>133623403</v>
       </c>
       <c r="B10" t="n">
-        <v>91920</v>
+        <v>79358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620268</v>
+        <v>620099</v>
       </c>
       <c r="R10" t="n">
-        <v>6898926</v>
+        <v>6898937</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -2844,32 +2844,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133623452</v>
+        <v>133623422</v>
       </c>
       <c r="B24" t="n">
-        <v>91920</v>
+        <v>80473</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620384</v>
+        <v>620275</v>
       </c>
       <c r="R24" t="n">
-        <v>6898898</v>
+        <v>6898953</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133623422</v>
+        <v>133623444</v>
       </c>
       <c r="B25" t="n">
-        <v>80473</v>
+        <v>91957</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2952,21 +2952,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620275</v>
+        <v>620341</v>
       </c>
       <c r="R25" t="n">
-        <v>6898953</v>
+        <v>6898817</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3038,32 +3038,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133623444</v>
+        <v>133623452</v>
       </c>
       <c r="B26" t="n">
-        <v>91957</v>
+        <v>91920</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620341</v>
+        <v>620384</v>
       </c>
       <c r="R26" t="n">
-        <v>6898817</v>
+        <v>6898898</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4132,32 +4132,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133623421</v>
+        <v>133623432</v>
       </c>
       <c r="B37" t="n">
-        <v>79390</v>
+        <v>91920</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620249</v>
+        <v>620266</v>
       </c>
       <c r="R37" t="n">
-        <v>6898992</v>
+        <v>6898927</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4229,32 +4229,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133623432</v>
+        <v>133623421</v>
       </c>
       <c r="B38" t="n">
-        <v>91920</v>
+        <v>79390</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4264,10 +4264,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>620266</v>
+        <v>620249</v>
       </c>
       <c r="R38" t="n">
-        <v>6898927</v>
+        <v>6898992</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -4132,32 +4132,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133623432</v>
+        <v>133623421</v>
       </c>
       <c r="B37" t="n">
-        <v>91920</v>
+        <v>79390</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620266</v>
+        <v>620249</v>
       </c>
       <c r="R37" t="n">
-        <v>6898927</v>
+        <v>6898992</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4229,32 +4229,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133623421</v>
+        <v>133623432</v>
       </c>
       <c r="B38" t="n">
-        <v>79390</v>
+        <v>91920</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4264,10 +4264,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>620249</v>
+        <v>620266</v>
       </c>
       <c r="R38" t="n">
-        <v>6898992</v>
+        <v>6898927</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133623415</v>
       </c>
       <c r="B2" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133623447</v>
+        <v>133623413</v>
       </c>
       <c r="B3" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620318</v>
+        <v>620178</v>
       </c>
       <c r="R3" t="n">
-        <v>6898875</v>
+        <v>6898953</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133623460</v>
+        <v>133623447</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620244</v>
+        <v>620318</v>
       </c>
       <c r="R4" t="n">
-        <v>6898934</v>
+        <v>6898875</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -945,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133623413</v>
+        <v>133623460</v>
       </c>
       <c r="B5" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,37 +977,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620178</v>
+        <v>620244</v>
       </c>
       <c r="R5" t="n">
-        <v>6898953</v>
+        <v>6898934</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1047,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133623435</v>
+        <v>133623403</v>
       </c>
       <c r="B6" t="n">
-        <v>79390</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620315</v>
+        <v>620099</v>
       </c>
       <c r="R6" t="n">
-        <v>6899013</v>
+        <v>6898937</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133623430</v>
+        <v>133623455</v>
       </c>
       <c r="B7" t="n">
-        <v>79390</v>
+        <v>91922</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620267</v>
+        <v>620268</v>
       </c>
       <c r="R7" t="n">
-        <v>6898931</v>
+        <v>6898926</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133623455</v>
+        <v>133623430</v>
       </c>
       <c r="B8" t="n">
-        <v>91920</v>
+        <v>79391</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620268</v>
+        <v>620267</v>
       </c>
       <c r="R8" t="n">
-        <v>6898926</v>
+        <v>6898931</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1367,7 +1367,7 @@
         <v>133623410</v>
       </c>
       <c r="B9" t="n">
-        <v>79390</v>
+        <v>79391</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133623403</v>
+        <v>133623435</v>
       </c>
       <c r="B10" t="n">
-        <v>79358</v>
+        <v>79391</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620099</v>
+        <v>620315</v>
       </c>
       <c r="R10" t="n">
-        <v>6898937</v>
+        <v>6899013</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1561,7 +1561,7 @@
         <v>133623407</v>
       </c>
       <c r="B11" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>133623409</v>
       </c>
       <c r="B13" t="n">
-        <v>79948</v>
+        <v>79949</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>133623429</v>
       </c>
       <c r="B14" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>133623436</v>
       </c>
       <c r="B15" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>133623434</v>
       </c>
       <c r="B16" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133623411</v>
+        <v>133623431</v>
       </c>
       <c r="B17" t="n">
-        <v>79390</v>
+        <v>79359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620166</v>
+        <v>620266</v>
       </c>
       <c r="R17" t="n">
-        <v>6898962</v>
+        <v>6898928</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2349,10 +2349,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133623431</v>
+        <v>133623411</v>
       </c>
       <c r="B19" t="n">
-        <v>79358</v>
+        <v>79391</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2360,21 +2360,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620266</v>
+        <v>620166</v>
       </c>
       <c r="R19" t="n">
-        <v>6898928</v>
+        <v>6898962</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2449,7 +2449,7 @@
         <v>133623443</v>
       </c>
       <c r="B20" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2543,10 +2543,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133623465</v>
+        <v>133623448</v>
       </c>
       <c r="B21" t="n">
-        <v>79977</v>
+        <v>57975</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2554,37 +2554,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620113</v>
+        <v>620324</v>
       </c>
       <c r="R21" t="n">
-        <v>6898932</v>
+        <v>6898861</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2614,6 +2619,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2640,10 +2650,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133623423</v>
+        <v>133623465</v>
       </c>
       <c r="B22" t="n">
-        <v>79358</v>
+        <v>79978</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,21 +2661,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2675,10 +2685,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620235</v>
+        <v>620113</v>
       </c>
       <c r="R22" t="n">
-        <v>6898952</v>
+        <v>6898932</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2737,10 +2747,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133623448</v>
+        <v>133623423</v>
       </c>
       <c r="B23" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,42 +2758,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620324</v>
+        <v>620235</v>
       </c>
       <c r="R23" t="n">
-        <v>6898861</v>
+        <v>6898952</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2813,11 +2818,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2844,32 +2844,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133623422</v>
+        <v>133623452</v>
       </c>
       <c r="B24" t="n">
-        <v>80473</v>
+        <v>91922</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620275</v>
+        <v>620384</v>
       </c>
       <c r="R24" t="n">
-        <v>6898953</v>
+        <v>6898898</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2941,10 +2941,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133623444</v>
+        <v>133623422</v>
       </c>
       <c r="B25" t="n">
-        <v>91957</v>
+        <v>80474</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2952,21 +2952,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620341</v>
+        <v>620275</v>
       </c>
       <c r="R25" t="n">
-        <v>6898817</v>
+        <v>6898953</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3038,32 +3038,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133623452</v>
+        <v>133623444</v>
       </c>
       <c r="B26" t="n">
-        <v>91920</v>
+        <v>91959</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620384</v>
+        <v>620341</v>
       </c>
       <c r="R26" t="n">
-        <v>6898898</v>
+        <v>6898817</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3135,7 +3135,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133623402</v>
+        <v>133623446</v>
       </c>
       <c r="B27" t="n">
         <v>57975</v>
@@ -3164,24 +3164,21 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620109</v>
+        <v>620339</v>
       </c>
       <c r="R27" t="n">
-        <v>6898948</v>
+        <v>6898847</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3240,10 +3237,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133623446</v>
+        <v>133623458</v>
       </c>
       <c r="B28" t="n">
-        <v>57975</v>
+        <v>91959</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3251,42 +3248,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620339</v>
+        <v>620239</v>
       </c>
       <c r="R28" t="n">
-        <v>6898847</v>
+        <v>6898916</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3342,45 +3334,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133623426</v>
+        <v>133623463</v>
       </c>
       <c r="B29" t="n">
-        <v>91920</v>
+        <v>92701</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>757</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620174</v>
+        <v>620142</v>
       </c>
       <c r="R29" t="n">
-        <v>6898936</v>
+        <v>6898946</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3415,12 +3410,18 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3439,10 +3440,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133623458</v>
+        <v>133623402</v>
       </c>
       <c r="B30" t="n">
-        <v>91957</v>
+        <v>57975</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3450,37 +3451,45 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620239</v>
+        <v>620109</v>
       </c>
       <c r="R30" t="n">
-        <v>6898916</v>
+        <v>6898948</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3536,48 +3545,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133623463</v>
+        <v>133623426</v>
       </c>
       <c r="B31" t="n">
-        <v>92699</v>
+        <v>91922</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>757</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620142</v>
+        <v>620174</v>
       </c>
       <c r="R31" t="n">
-        <v>6898946</v>
+        <v>6898936</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3612,18 +3618,12 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133623459</v>
+        <v>133623433</v>
       </c>
       <c r="B32" t="n">
-        <v>81340</v>
+        <v>83336</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3653,21 +3653,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1049</v>
+        <v>308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620266</v>
+        <v>620290</v>
       </c>
       <c r="R32" t="n">
-        <v>6898988</v>
+        <v>6898929</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3739,10 +3739,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133623462</v>
+        <v>133623438</v>
       </c>
       <c r="B33" t="n">
-        <v>92699</v>
+        <v>79025</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3750,21 +3750,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>757</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620130</v>
+        <v>620335</v>
       </c>
       <c r="R33" t="n">
-        <v>6898930</v>
+        <v>6898933</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3810,11 +3810,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar. Röd KOH-reaktion</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3841,32 +3836,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133623433</v>
+        <v>133623464</v>
       </c>
       <c r="B34" t="n">
-        <v>83335</v>
+        <v>91922</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3876,10 +3871,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>620290</v>
+        <v>620127</v>
       </c>
       <c r="R34" t="n">
-        <v>6898929</v>
+        <v>6898927</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3938,10 +3933,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133623438</v>
+        <v>133623462</v>
       </c>
       <c r="B35" t="n">
-        <v>79024</v>
+        <v>92701</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3949,21 +3944,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>757</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3973,10 +3968,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>620335</v>
+        <v>620130</v>
       </c>
       <c r="R35" t="n">
-        <v>6898933</v>
+        <v>6898930</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4009,6 +4004,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar. Röd KOH-reaktion</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4035,32 +4035,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133623464</v>
+        <v>133623459</v>
       </c>
       <c r="B36" t="n">
-        <v>91920</v>
+        <v>81341</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>1049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620127</v>
+        <v>620266</v>
       </c>
       <c r="R36" t="n">
-        <v>6898927</v>
+        <v>6898988</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4135,7 +4135,7 @@
         <v>133623421</v>
       </c>
       <c r="B37" t="n">
-        <v>79390</v>
+        <v>79391</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>133623432</v>
       </c>
       <c r="B38" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>133623437</v>
       </c>
       <c r="B39" t="n">
-        <v>79977</v>
+        <v>79978</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>133623404</v>
       </c>
       <c r="B41" t="n">
-        <v>79390</v>
+        <v>79391</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>133623428</v>
       </c>
       <c r="B42" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>133623424</v>
       </c>
       <c r="B43" t="n">
-        <v>79977</v>
+        <v>79978</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>133623412</v>
       </c>
       <c r="B44" t="n">
-        <v>79390</v>
+        <v>79391</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>133623439</v>
       </c>
       <c r="B45" t="n">
-        <v>79390</v>
+        <v>79391</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5010,10 +5010,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133623453</v>
+        <v>133623445</v>
       </c>
       <c r="B46" t="n">
-        <v>79358</v>
+        <v>91959</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5021,21 +5021,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>620262</v>
+        <v>620349</v>
       </c>
       <c r="R46" t="n">
-        <v>6898935</v>
+        <v>6898830</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5107,10 +5107,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133623445</v>
+        <v>133623425</v>
       </c>
       <c r="B47" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5142,10 +5142,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>620349</v>
+        <v>620196</v>
       </c>
       <c r="R47" t="n">
-        <v>6898830</v>
+        <v>6898959</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5204,10 +5204,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133623417</v>
+        <v>133623453</v>
       </c>
       <c r="B48" t="n">
-        <v>80473</v>
+        <v>79359</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5215,21 +5215,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620220</v>
+        <v>620262</v>
       </c>
       <c r="R48" t="n">
-        <v>6898975</v>
+        <v>6898935</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5301,10 +5301,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133623425</v>
+        <v>133623417</v>
       </c>
       <c r="B49" t="n">
-        <v>91957</v>
+        <v>80474</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5312,21 +5312,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>620196</v>
+        <v>620220</v>
       </c>
       <c r="R49" t="n">
-        <v>6898959</v>
+        <v>6898975</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5401,7 +5401,7 @@
         <v>133623466</v>
       </c>
       <c r="B50" t="n">
-        <v>91978</v>
+        <v>91980</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>133623456</v>
       </c>
       <c r="B51" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133623403</v>
+        <v>133623435</v>
       </c>
       <c r="B6" t="n">
-        <v>79359</v>
+        <v>79391</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620099</v>
+        <v>620315</v>
       </c>
       <c r="R6" t="n">
-        <v>6898937</v>
+        <v>6899013</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133623455</v>
+        <v>133623403</v>
       </c>
       <c r="B7" t="n">
-        <v>91922</v>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620268</v>
+        <v>620099</v>
       </c>
       <c r="R7" t="n">
-        <v>6898926</v>
+        <v>6898937</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133623435</v>
+        <v>133623455</v>
       </c>
       <c r="B10" t="n">
-        <v>79391</v>
+        <v>91922</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620315</v>
+        <v>620268</v>
       </c>
       <c r="R10" t="n">
-        <v>6899013</v>
+        <v>6898926</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -2446,10 +2446,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133623443</v>
+        <v>133623465</v>
       </c>
       <c r="B20" t="n">
-        <v>79359</v>
+        <v>79978</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2457,21 +2457,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620349</v>
+        <v>620113</v>
       </c>
       <c r="R20" t="n">
-        <v>6898850</v>
+        <v>6898932</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2543,10 +2543,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133623448</v>
+        <v>133623443</v>
       </c>
       <c r="B21" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2554,42 +2554,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620324</v>
+        <v>620349</v>
       </c>
       <c r="R21" t="n">
-        <v>6898861</v>
+        <v>6898850</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2619,11 +2614,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2650,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133623465</v>
+        <v>133623423</v>
       </c>
       <c r="B22" t="n">
-        <v>79978</v>
+        <v>79359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2661,21 +2651,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2685,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620113</v>
+        <v>620235</v>
       </c>
       <c r="R22" t="n">
-        <v>6898932</v>
+        <v>6898952</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2747,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133623423</v>
+        <v>133623448</v>
       </c>
       <c r="B23" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2758,37 +2748,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620235</v>
+        <v>620324</v>
       </c>
       <c r="R23" t="n">
-        <v>6898952</v>
+        <v>6898861</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2818,6 +2813,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3135,7 +3135,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133623446</v>
+        <v>133623402</v>
       </c>
       <c r="B27" t="n">
         <v>57975</v>
@@ -3164,21 +3164,24 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620339</v>
+        <v>620109</v>
       </c>
       <c r="R27" t="n">
-        <v>6898847</v>
+        <v>6898948</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3237,10 +3240,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133623458</v>
+        <v>133623446</v>
       </c>
       <c r="B28" t="n">
-        <v>91959</v>
+        <v>57975</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3248,37 +3251,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620239</v>
+        <v>620339</v>
       </c>
       <c r="R28" t="n">
-        <v>6898916</v>
+        <v>6898847</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3334,48 +3342,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133623463</v>
+        <v>133623426</v>
       </c>
       <c r="B29" t="n">
-        <v>92701</v>
+        <v>91922</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>757</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620142</v>
+        <v>620174</v>
       </c>
       <c r="R29" t="n">
-        <v>6898946</v>
+        <v>6898936</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3410,18 +3415,12 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3440,10 +3439,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133623402</v>
+        <v>133623458</v>
       </c>
       <c r="B30" t="n">
-        <v>57975</v>
+        <v>91959</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3451,45 +3450,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620109</v>
+        <v>620239</v>
       </c>
       <c r="R30" t="n">
-        <v>6898948</v>
+        <v>6898916</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3545,45 +3536,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133623426</v>
+        <v>133623463</v>
       </c>
       <c r="B31" t="n">
-        <v>91922</v>
+        <v>92701</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>757</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620174</v>
+        <v>620142</v>
       </c>
       <c r="R31" t="n">
-        <v>6898936</v>
+        <v>6898946</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3618,12 +3612,18 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133623433</v>
+        <v>133623462</v>
       </c>
       <c r="B32" t="n">
-        <v>83336</v>
+        <v>92701</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3653,21 +3653,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>757</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620290</v>
+        <v>620130</v>
       </c>
       <c r="R32" t="n">
-        <v>6898929</v>
+        <v>6898930</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3713,6 +3713,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar. Röd KOH-reaktion</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3739,10 +3744,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133623438</v>
+        <v>133623433</v>
       </c>
       <c r="B33" t="n">
-        <v>79025</v>
+        <v>83336</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3750,21 +3755,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3774,10 +3779,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620335</v>
+        <v>620290</v>
       </c>
       <c r="R33" t="n">
-        <v>6898933</v>
+        <v>6898929</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3836,32 +3841,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133623464</v>
+        <v>133623438</v>
       </c>
       <c r="B34" t="n">
-        <v>91922</v>
+        <v>79025</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3871,10 +3876,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>620127</v>
+        <v>620335</v>
       </c>
       <c r="R34" t="n">
-        <v>6898927</v>
+        <v>6898933</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3933,32 +3938,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133623462</v>
+        <v>133623464</v>
       </c>
       <c r="B35" t="n">
-        <v>92701</v>
+        <v>91922</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>757</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3968,10 +3973,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>620130</v>
+        <v>620127</v>
       </c>
       <c r="R35" t="n">
-        <v>6898930</v>
+        <v>6898927</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4004,11 +4009,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar. Röd KOH-reaktion</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4132,32 +4132,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133623421</v>
+        <v>133623432</v>
       </c>
       <c r="B37" t="n">
-        <v>79391</v>
+        <v>91922</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620249</v>
+        <v>620266</v>
       </c>
       <c r="R37" t="n">
-        <v>6898992</v>
+        <v>6898927</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4229,32 +4229,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133623432</v>
+        <v>133623421</v>
       </c>
       <c r="B38" t="n">
-        <v>91922</v>
+        <v>79391</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4264,10 +4264,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>620266</v>
+        <v>620249</v>
       </c>
       <c r="R38" t="n">
-        <v>6898927</v>
+        <v>6898992</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5010,7 +5010,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133623445</v>
+        <v>133623425</v>
       </c>
       <c r="B46" t="n">
         <v>91959</v>
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>620349</v>
+        <v>620196</v>
       </c>
       <c r="R46" t="n">
-        <v>6898830</v>
+        <v>6898959</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5107,7 +5107,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133623425</v>
+        <v>133623445</v>
       </c>
       <c r="B47" t="n">
         <v>91959</v>
@@ -5142,10 +5142,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>620196</v>
+        <v>620349</v>
       </c>
       <c r="R47" t="n">
-        <v>6898959</v>
+        <v>6898830</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -675,48 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133623415</v>
+        <v>133623460</v>
       </c>
       <c r="B2" t="n">
-        <v>91923</v>
+        <v>57975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620235</v>
+        <v>620244</v>
       </c>
       <c r="R2" t="n">
-        <v>6898961</v>
+        <v>6898934</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -869,53 +879,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133623460</v>
+        <v>133623415</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620244</v>
+        <v>620235</v>
       </c>
       <c r="R4" t="n">
-        <v>6898934</v>
+        <v>6898961</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -945,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1073,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133623435</v>
+        <v>133623430</v>
       </c>
       <c r="B6" t="n">
         <v>79391</v>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620315</v>
+        <v>620267</v>
       </c>
       <c r="R6" t="n">
-        <v>6899013</v>
+        <v>6898931</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133623430</v>
+        <v>133623403</v>
       </c>
       <c r="B7" t="n">
-        <v>79391</v>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620267</v>
+        <v>620099</v>
       </c>
       <c r="R7" t="n">
-        <v>6898931</v>
+        <v>6898937</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133623410</v>
+        <v>133623455</v>
       </c>
       <c r="B8" t="n">
-        <v>79391</v>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620159</v>
+        <v>620268</v>
       </c>
       <c r="R8" t="n">
-        <v>6898960</v>
+        <v>6898926</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133623455</v>
+        <v>133623435</v>
       </c>
       <c r="B9" t="n">
-        <v>91923</v>
+        <v>79391</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620268</v>
+        <v>620315</v>
       </c>
       <c r="R9" t="n">
-        <v>6898926</v>
+        <v>6899013</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133623403</v>
+        <v>133623410</v>
       </c>
       <c r="B10" t="n">
-        <v>79359</v>
+        <v>79391</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620099</v>
+        <v>620159</v>
       </c>
       <c r="R10" t="n">
-        <v>6898937</v>
+        <v>6898960</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -2145,45 +2145,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133623431</v>
+        <v>133623442</v>
       </c>
       <c r="B17" t="n">
-        <v>79359</v>
+        <v>4776</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620266</v>
+        <v>620347</v>
       </c>
       <c r="R17" t="n">
-        <v>6898928</v>
+        <v>6898852</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2224,6 +2233,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2242,54 +2252,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133623442</v>
+        <v>133623431</v>
       </c>
       <c r="B18" t="n">
-        <v>4776</v>
+        <v>79359</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620347</v>
+        <v>620266</v>
       </c>
       <c r="R18" t="n">
-        <v>6898852</v>
+        <v>6898928</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2330,7 +2331,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2446,10 +2446,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133623443</v>
+        <v>133623465</v>
       </c>
       <c r="B20" t="n">
-        <v>79359</v>
+        <v>79978</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2457,21 +2457,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620349</v>
+        <v>620113</v>
       </c>
       <c r="R20" t="n">
-        <v>6898850</v>
+        <v>6898932</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2543,7 +2543,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133623423</v>
+        <v>133623443</v>
       </c>
       <c r="B21" t="n">
         <v>79359</v>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620235</v>
+        <v>620349</v>
       </c>
       <c r="R21" t="n">
-        <v>6898952</v>
+        <v>6898850</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2640,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133623448</v>
+        <v>133623423</v>
       </c>
       <c r="B22" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,42 +2651,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620324</v>
+        <v>620235</v>
       </c>
       <c r="R22" t="n">
-        <v>6898861</v>
+        <v>6898952</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2716,11 +2711,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2747,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133623465</v>
+        <v>133623448</v>
       </c>
       <c r="B23" t="n">
-        <v>79978</v>
+        <v>57975</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2758,37 +2748,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620113</v>
+        <v>620324</v>
       </c>
       <c r="R23" t="n">
-        <v>6898932</v>
+        <v>6898861</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2818,6 +2813,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2844,32 +2844,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133623452</v>
+        <v>133623444</v>
       </c>
       <c r="B24" t="n">
-        <v>91923</v>
+        <v>91960</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620384</v>
+        <v>620341</v>
       </c>
       <c r="R24" t="n">
-        <v>6898898</v>
+        <v>6898817</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2941,32 +2941,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133623422</v>
+        <v>133623452</v>
       </c>
       <c r="B25" t="n">
-        <v>80474</v>
+        <v>91923</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620275</v>
+        <v>620384</v>
       </c>
       <c r="R25" t="n">
-        <v>6898953</v>
+        <v>6898898</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3038,10 +3038,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133623444</v>
+        <v>133623422</v>
       </c>
       <c r="B26" t="n">
-        <v>91960</v>
+        <v>80474</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3049,21 +3049,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620341</v>
+        <v>620275</v>
       </c>
       <c r="R26" t="n">
-        <v>6898817</v>
+        <v>6898953</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3135,48 +3135,56 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133623426</v>
+        <v>133623402</v>
       </c>
       <c r="B27" t="n">
-        <v>91923</v>
+        <v>57975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620174</v>
+        <v>620109</v>
       </c>
       <c r="R27" t="n">
-        <v>6898936</v>
+        <v>6898948</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3232,7 +3240,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133623402</v>
+        <v>133623446</v>
       </c>
       <c r="B28" t="n">
         <v>57975</v>
@@ -3261,24 +3269,21 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620109</v>
+        <v>620339</v>
       </c>
       <c r="R28" t="n">
-        <v>6898948</v>
+        <v>6898847</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3337,53 +3342,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133623446</v>
+        <v>133623426</v>
       </c>
       <c r="B29" t="n">
-        <v>57975</v>
+        <v>91923</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620339</v>
+        <v>620174</v>
       </c>
       <c r="R29" t="n">
-        <v>6898847</v>
+        <v>6898936</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133623462</v>
+        <v>133623433</v>
       </c>
       <c r="B32" t="n">
-        <v>92702</v>
+        <v>83336</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3653,21 +3653,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>757</v>
+        <v>308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620130</v>
+        <v>620290</v>
       </c>
       <c r="R32" t="n">
-        <v>6898930</v>
+        <v>6898929</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3713,11 +3713,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar. Röd KOH-reaktion</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3744,10 +3739,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133623433</v>
+        <v>133623459</v>
       </c>
       <c r="B33" t="n">
-        <v>83336</v>
+        <v>81341</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3755,21 +3750,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>1049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3779,10 +3774,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620290</v>
+        <v>620266</v>
       </c>
       <c r="R33" t="n">
-        <v>6898929</v>
+        <v>6898988</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3841,10 +3836,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133623438</v>
+        <v>133623462</v>
       </c>
       <c r="B34" t="n">
-        <v>79025</v>
+        <v>92702</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3852,21 +3847,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>757</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3876,10 +3871,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>620335</v>
+        <v>620130</v>
       </c>
       <c r="R34" t="n">
-        <v>6898933</v>
+        <v>6898930</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3912,6 +3907,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar. Röd KOH-reaktion</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4035,10 +4035,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133623459</v>
+        <v>133623438</v>
       </c>
       <c r="B36" t="n">
-        <v>81341</v>
+        <v>79025</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4046,21 +4046,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620266</v>
+        <v>620335</v>
       </c>
       <c r="R36" t="n">
-        <v>6898988</v>
+        <v>6898933</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4326,10 +4326,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133623437</v>
+        <v>133623408</v>
       </c>
       <c r="B39" t="n">
-        <v>79978</v>
+        <v>57975</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4337,37 +4337,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>620340</v>
+        <v>620156</v>
       </c>
       <c r="R39" t="n">
-        <v>6898950</v>
+        <v>6898981</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4423,10 +4428,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133623408</v>
+        <v>133623437</v>
       </c>
       <c r="B40" t="n">
-        <v>57975</v>
+        <v>79978</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4434,42 +4439,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>620156</v>
+        <v>620340</v>
       </c>
       <c r="R40" t="n">
-        <v>6898981</v>
+        <v>6898950</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4525,10 +4525,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133623404</v>
+        <v>133623424</v>
       </c>
       <c r="B41" t="n">
-        <v>79391</v>
+        <v>79978</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4536,21 +4536,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>620098</v>
+        <v>620238</v>
       </c>
       <c r="R41" t="n">
         <v>6898939</v>
@@ -4622,10 +4622,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133623428</v>
+        <v>133623404</v>
       </c>
       <c r="B42" t="n">
-        <v>91960</v>
+        <v>79391</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4633,21 +4633,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4657,10 +4657,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620196</v>
+        <v>620098</v>
       </c>
       <c r="R42" t="n">
-        <v>6898931</v>
+        <v>6898939</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4719,10 +4719,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133623424</v>
+        <v>133623428</v>
       </c>
       <c r="B43" t="n">
-        <v>79978</v>
+        <v>91960</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4730,21 +4730,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4754,10 +4754,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620238</v>
+        <v>620196</v>
       </c>
       <c r="R43" t="n">
-        <v>6898939</v>
+        <v>6898931</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5010,10 +5010,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133623425</v>
+        <v>133623453</v>
       </c>
       <c r="B46" t="n">
-        <v>91960</v>
+        <v>79359</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5021,21 +5021,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>620196</v>
+        <v>620262</v>
       </c>
       <c r="R46" t="n">
-        <v>6898959</v>
+        <v>6898935</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5204,10 +5204,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133623453</v>
+        <v>133623417</v>
       </c>
       <c r="B48" t="n">
-        <v>79359</v>
+        <v>80474</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5215,21 +5215,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620262</v>
+        <v>620220</v>
       </c>
       <c r="R48" t="n">
-        <v>6898935</v>
+        <v>6898975</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5301,10 +5301,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133623417</v>
+        <v>133623425</v>
       </c>
       <c r="B49" t="n">
-        <v>80474</v>
+        <v>91960</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5312,21 +5312,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>620220</v>
+        <v>620196</v>
       </c>
       <c r="R49" t="n">
-        <v>6898975</v>
+        <v>6898959</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5398,10 +5398,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133623466</v>
+        <v>133623456</v>
       </c>
       <c r="B50" t="n">
-        <v>91981</v>
+        <v>91960</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5409,21 +5409,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5433,10 +5433,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>620116</v>
+        <v>620264</v>
       </c>
       <c r="R50" t="n">
-        <v>6898986</v>
+        <v>6898924</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5495,10 +5495,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133623456</v>
+        <v>133623466</v>
       </c>
       <c r="B51" t="n">
-        <v>91960</v>
+        <v>91981</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5506,21 +5506,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>620264</v>
+        <v>620116</v>
       </c>
       <c r="R51" t="n">
-        <v>6898924</v>
+        <v>6898986</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133623460</v>
+        <v>133623415</v>
       </c>
       <c r="B2" t="n">
-        <v>57975</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620244</v>
+        <v>620235</v>
       </c>
       <c r="R2" t="n">
-        <v>6898934</v>
+        <v>6898961</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133623413</v>
+        <v>133623447</v>
       </c>
       <c r="B3" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620178</v>
+        <v>620318</v>
       </c>
       <c r="R3" t="n">
-        <v>6898953</v>
+        <v>6898875</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,48 +869,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133623415</v>
+        <v>133623460</v>
       </c>
       <c r="B4" t="n">
-        <v>91923</v>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620235</v>
+        <v>620244</v>
       </c>
       <c r="R4" t="n">
-        <v>6898961</v>
+        <v>6898934</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -950,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133623447</v>
+        <v>133623413</v>
       </c>
       <c r="B5" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620318</v>
+        <v>620178</v>
       </c>
       <c r="R5" t="n">
-        <v>6898875</v>
+        <v>6898953</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1076,7 +1076,7 @@
         <v>133623430</v>
       </c>
       <c r="B6" t="n">
-        <v>79391</v>
+        <v>79398</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133623403</v>
+        <v>133623410</v>
       </c>
       <c r="B7" t="n">
-        <v>79359</v>
+        <v>79398</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620099</v>
+        <v>620159</v>
       </c>
       <c r="R7" t="n">
-        <v>6898937</v>
+        <v>6898960</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1270,7 +1270,7 @@
         <v>133623455</v>
       </c>
       <c r="B8" t="n">
-        <v>91923</v>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>133623435</v>
       </c>
       <c r="B9" t="n">
-        <v>79391</v>
+        <v>79398</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133623410</v>
+        <v>133623403</v>
       </c>
       <c r="B10" t="n">
-        <v>79391</v>
+        <v>79366</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620159</v>
+        <v>620099</v>
       </c>
       <c r="R10" t="n">
-        <v>6898960</v>
+        <v>6898937</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1561,7 +1561,7 @@
         <v>133623407</v>
       </c>
       <c r="B11" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133623429</v>
+        <v>133623409</v>
       </c>
       <c r="B13" t="n">
-        <v>91960</v>
+        <v>79956</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620275</v>
+        <v>620161</v>
       </c>
       <c r="R13" t="n">
-        <v>6898905</v>
+        <v>6898969</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133623409</v>
+        <v>133623429</v>
       </c>
       <c r="B14" t="n">
-        <v>79949</v>
+        <v>91967</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1865,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620161</v>
+        <v>620275</v>
       </c>
       <c r="R14" t="n">
-        <v>6898969</v>
+        <v>6898905</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1954,7 +1954,7 @@
         <v>133623436</v>
       </c>
       <c r="B15" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>133623434</v>
       </c>
       <c r="B16" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2145,54 +2145,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133623442</v>
+        <v>133623411</v>
       </c>
       <c r="B17" t="n">
-        <v>4776</v>
+        <v>79398</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100299</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620347</v>
+        <v>620166</v>
       </c>
       <c r="R17" t="n">
-        <v>6898852</v>
+        <v>6898962</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2233,7 +2224,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2252,45 +2242,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133623431</v>
+        <v>133623442</v>
       </c>
       <c r="B18" t="n">
-        <v>79359</v>
+        <v>4776</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620266</v>
+        <v>620347</v>
       </c>
       <c r="R18" t="n">
-        <v>6898928</v>
+        <v>6898852</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2331,6 +2330,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2349,10 +2349,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133623411</v>
+        <v>133623431</v>
       </c>
       <c r="B19" t="n">
-        <v>79391</v>
+        <v>79366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2360,21 +2360,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620166</v>
+        <v>620266</v>
       </c>
       <c r="R19" t="n">
-        <v>6898962</v>
+        <v>6898928</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2446,10 +2446,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133623465</v>
+        <v>133623443</v>
       </c>
       <c r="B20" t="n">
-        <v>79978</v>
+        <v>79366</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2457,21 +2457,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620113</v>
+        <v>620349</v>
       </c>
       <c r="R20" t="n">
-        <v>6898932</v>
+        <v>6898850</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2543,10 +2543,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133623443</v>
+        <v>133623465</v>
       </c>
       <c r="B21" t="n">
-        <v>79359</v>
+        <v>79985</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2554,21 +2554,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620349</v>
+        <v>620113</v>
       </c>
       <c r="R21" t="n">
-        <v>6898850</v>
+        <v>6898932</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2643,7 +2643,7 @@
         <v>133623423</v>
       </c>
       <c r="B22" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,32 +2844,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133623444</v>
+        <v>133623452</v>
       </c>
       <c r="B24" t="n">
-        <v>91960</v>
+        <v>91930</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620341</v>
+        <v>620384</v>
       </c>
       <c r="R24" t="n">
-        <v>6898817</v>
+        <v>6898898</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2941,32 +2941,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133623452</v>
+        <v>133623422</v>
       </c>
       <c r="B25" t="n">
-        <v>91923</v>
+        <v>80481</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620384</v>
+        <v>620275</v>
       </c>
       <c r="R25" t="n">
-        <v>6898898</v>
+        <v>6898953</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3038,10 +3038,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133623422</v>
+        <v>133623444</v>
       </c>
       <c r="B26" t="n">
-        <v>80474</v>
+        <v>91967</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3049,21 +3049,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620275</v>
+        <v>620341</v>
       </c>
       <c r="R26" t="n">
-        <v>6898953</v>
+        <v>6898817</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3345,7 +3345,7 @@
         <v>133623426</v>
       </c>
       <c r="B29" t="n">
-        <v>91923</v>
+        <v>91930</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133623458</v>
+        <v>133623463</v>
       </c>
       <c r="B30" t="n">
-        <v>91960</v>
+        <v>92709</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3450,34 +3450,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>757</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620239</v>
+        <v>620142</v>
       </c>
       <c r="R30" t="n">
-        <v>6898916</v>
+        <v>6898946</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3512,12 +3515,18 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3536,10 +3545,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133623463</v>
+        <v>133623458</v>
       </c>
       <c r="B31" t="n">
-        <v>92702</v>
+        <v>91967</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3547,37 +3556,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>757</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620142</v>
+        <v>620239</v>
       </c>
       <c r="R31" t="n">
-        <v>6898946</v>
+        <v>6898916</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3612,18 +3618,12 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133623433</v>
+        <v>133623462</v>
       </c>
       <c r="B32" t="n">
-        <v>83336</v>
+        <v>92709</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3653,21 +3653,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>308</v>
+        <v>757</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620290</v>
+        <v>620130</v>
       </c>
       <c r="R32" t="n">
-        <v>6898929</v>
+        <v>6898930</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3713,6 +3713,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar. Röd KOH-reaktion</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3739,10 +3744,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133623459</v>
+        <v>133623438</v>
       </c>
       <c r="B33" t="n">
-        <v>81341</v>
+        <v>79032</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3750,21 +3755,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3774,10 +3779,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620266</v>
+        <v>620335</v>
       </c>
       <c r="R33" t="n">
-        <v>6898988</v>
+        <v>6898933</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3836,10 +3841,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133623462</v>
+        <v>133623433</v>
       </c>
       <c r="B34" t="n">
-        <v>92702</v>
+        <v>83343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3847,21 +3852,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>757</v>
+        <v>308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3871,10 +3876,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>620130</v>
+        <v>620290</v>
       </c>
       <c r="R34" t="n">
-        <v>6898930</v>
+        <v>6898929</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3907,11 +3912,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar. Röd KOH-reaktion</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3938,32 +3938,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133623464</v>
+        <v>133623459</v>
       </c>
       <c r="B35" t="n">
-        <v>91923</v>
+        <v>81348</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>1049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3973,10 +3973,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>620127</v>
+        <v>620266</v>
       </c>
       <c r="R35" t="n">
-        <v>6898927</v>
+        <v>6898988</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4035,32 +4035,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133623438</v>
+        <v>133623464</v>
       </c>
       <c r="B36" t="n">
-        <v>79025</v>
+        <v>91930</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620335</v>
+        <v>620127</v>
       </c>
       <c r="R36" t="n">
-        <v>6898933</v>
+        <v>6898927</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4132,32 +4132,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133623432</v>
+        <v>133623421</v>
       </c>
       <c r="B37" t="n">
-        <v>91923</v>
+        <v>79398</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620266</v>
+        <v>620249</v>
       </c>
       <c r="R37" t="n">
-        <v>6898927</v>
+        <v>6898992</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4229,32 +4229,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133623421</v>
+        <v>133623432</v>
       </c>
       <c r="B38" t="n">
-        <v>79391</v>
+        <v>91930</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4264,10 +4264,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>620249</v>
+        <v>620266</v>
       </c>
       <c r="R38" t="n">
-        <v>6898992</v>
+        <v>6898927</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4326,10 +4326,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133623408</v>
+        <v>133623437</v>
       </c>
       <c r="B39" t="n">
-        <v>57975</v>
+        <v>79985</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4337,42 +4337,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>620156</v>
+        <v>620340</v>
       </c>
       <c r="R39" t="n">
-        <v>6898981</v>
+        <v>6898950</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4428,10 +4423,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133623437</v>
+        <v>133623408</v>
       </c>
       <c r="B40" t="n">
-        <v>79978</v>
+        <v>57975</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4439,37 +4434,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>620340</v>
+        <v>620156</v>
       </c>
       <c r="R40" t="n">
-        <v>6898950</v>
+        <v>6898981</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>133623424</v>
       </c>
       <c r="B41" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4622,10 +4622,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133623404</v>
+        <v>133623428</v>
       </c>
       <c r="B42" t="n">
-        <v>79391</v>
+        <v>91967</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4633,21 +4633,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4657,10 +4657,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620098</v>
+        <v>620196</v>
       </c>
       <c r="R42" t="n">
-        <v>6898939</v>
+        <v>6898931</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4719,10 +4719,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133623428</v>
+        <v>133623404</v>
       </c>
       <c r="B43" t="n">
-        <v>91960</v>
+        <v>79398</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4730,21 +4730,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4754,10 +4754,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620196</v>
+        <v>620098</v>
       </c>
       <c r="R43" t="n">
-        <v>6898931</v>
+        <v>6898939</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4816,10 +4816,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133623412</v>
+        <v>133623439</v>
       </c>
       <c r="B44" t="n">
-        <v>79391</v>
+        <v>79398</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>620162</v>
+        <v>620336</v>
       </c>
       <c r="R44" t="n">
-        <v>6899008</v>
+        <v>6898875</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4913,10 +4913,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133623439</v>
+        <v>133623412</v>
       </c>
       <c r="B45" t="n">
-        <v>79391</v>
+        <v>79398</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4948,10 +4948,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>620336</v>
+        <v>620162</v>
       </c>
       <c r="R45" t="n">
-        <v>6898875</v>
+        <v>6899008</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5010,10 +5010,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133623453</v>
+        <v>133623445</v>
       </c>
       <c r="B46" t="n">
-        <v>79359</v>
+        <v>91967</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5021,21 +5021,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>620262</v>
+        <v>620349</v>
       </c>
       <c r="R46" t="n">
-        <v>6898935</v>
+        <v>6898830</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5107,10 +5107,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133623445</v>
+        <v>133623417</v>
       </c>
       <c r="B47" t="n">
-        <v>91960</v>
+        <v>80481</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5118,21 +5118,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5142,10 +5142,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>620349</v>
+        <v>620220</v>
       </c>
       <c r="R47" t="n">
-        <v>6898830</v>
+        <v>6898975</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5204,10 +5204,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133623417</v>
+        <v>133623425</v>
       </c>
       <c r="B48" t="n">
-        <v>80474</v>
+        <v>91967</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5215,21 +5215,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620220</v>
+        <v>620196</v>
       </c>
       <c r="R48" t="n">
-        <v>6898975</v>
+        <v>6898959</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5301,10 +5301,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133623425</v>
+        <v>133623453</v>
       </c>
       <c r="B49" t="n">
-        <v>91960</v>
+        <v>79366</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5312,21 +5312,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>620196</v>
+        <v>620262</v>
       </c>
       <c r="R49" t="n">
-        <v>6898959</v>
+        <v>6898935</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5398,10 +5398,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133623456</v>
+        <v>133623466</v>
       </c>
       <c r="B50" t="n">
-        <v>91960</v>
+        <v>91988</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5409,21 +5409,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5433,10 +5433,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>620264</v>
+        <v>620116</v>
       </c>
       <c r="R50" t="n">
-        <v>6898924</v>
+        <v>6898986</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5495,10 +5495,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133623466</v>
+        <v>133623456</v>
       </c>
       <c r="B51" t="n">
-        <v>91981</v>
+        <v>91967</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5506,21 +5506,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>620116</v>
+        <v>620264</v>
       </c>
       <c r="R51" t="n">
-        <v>6898986</v>
+        <v>6898924</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>

--- a/artfynd/A 16264-2026 artfynd.xlsx
+++ b/artfynd/A 16264-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133623415</v>
+        <v>133623404</v>
       </c>
       <c r="B2" t="n">
-        <v>91930</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620235</v>
+        <v>620098</v>
       </c>
       <c r="R2" t="n">
-        <v>6898961</v>
+        <v>6898939</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133623447</v>
+        <v>133623406</v>
       </c>
       <c r="B3" t="n">
-        <v>79366</v>
+        <v>79405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620318</v>
+        <v>620115</v>
       </c>
       <c r="R3" t="n">
-        <v>6898875</v>
+        <v>6899002</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133623460</v>
+        <v>133623410</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>79405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620244</v>
+        <v>620159</v>
       </c>
       <c r="R4" t="n">
-        <v>6898934</v>
+        <v>6898960</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -945,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133623413</v>
+        <v>133623411</v>
       </c>
       <c r="B5" t="n">
-        <v>79366</v>
+        <v>79405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620178</v>
+        <v>620166</v>
       </c>
       <c r="R5" t="n">
-        <v>6898953</v>
+        <v>6898962</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1073,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133623430</v>
+        <v>133623412</v>
       </c>
       <c r="B6" t="n">
-        <v>79398</v>
+        <v>79405</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620267</v>
+        <v>620162</v>
       </c>
       <c r="R6" t="n">
-        <v>6898931</v>
+        <v>6899008</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1170,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133623410</v>
+        <v>133623421</v>
       </c>
       <c r="B7" t="n">
-        <v>79398</v>
+        <v>79405</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620159</v>
+        <v>620249</v>
       </c>
       <c r="R7" t="n">
-        <v>6898960</v>
+        <v>6898992</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1267,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133623455</v>
+        <v>133623430</v>
       </c>
       <c r="B8" t="n">
-        <v>91930</v>
+        <v>79405</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620268</v>
+        <v>620267</v>
       </c>
       <c r="R8" t="n">
-        <v>6898926</v>
+        <v>6898931</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1367,7 +1357,7 @@
         <v>133623435</v>
       </c>
       <c r="B9" t="n">
-        <v>79398</v>
+        <v>79405</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133623403</v>
+        <v>133623439</v>
       </c>
       <c r="B10" t="n">
-        <v>79366</v>
+        <v>79405</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620099</v>
+        <v>620336</v>
       </c>
       <c r="R10" t="n">
-        <v>6898937</v>
+        <v>6898875</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1558,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133623407</v>
+        <v>133623433</v>
       </c>
       <c r="B11" t="n">
-        <v>79366</v>
+        <v>83350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620142</v>
+        <v>620290</v>
       </c>
       <c r="R11" t="n">
-        <v>6898988</v>
+        <v>6898929</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1655,50 +1645,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133623440</v>
+        <v>133623438</v>
       </c>
       <c r="B12" t="n">
-        <v>5181</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620348</v>
+        <v>620335</v>
       </c>
       <c r="R12" t="n">
-        <v>6898859</v>
+        <v>6898933</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1757,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133623409</v>
+        <v>133623462</v>
       </c>
       <c r="B13" t="n">
-        <v>79956</v>
+        <v>92716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>757</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620161</v>
+        <v>620130</v>
       </c>
       <c r="R13" t="n">
-        <v>6898969</v>
+        <v>6898930</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1828,6 +1813,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar. Röd KOH-reaktion</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1854,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133623429</v>
+        <v>133623463</v>
       </c>
       <c r="B14" t="n">
-        <v>91967</v>
+        <v>92716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,34 +1855,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>757</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620275</v>
+        <v>620142</v>
       </c>
       <c r="R14" t="n">
-        <v>6898905</v>
+        <v>6898946</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1927,12 +1920,18 @@
           <t>2026-05-19</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1951,10 +1950,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133623436</v>
+        <v>133623459</v>
       </c>
       <c r="B15" t="n">
-        <v>91967</v>
+        <v>81355</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,21 +1961,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1985,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620349</v>
+        <v>620266</v>
       </c>
       <c r="R15" t="n">
-        <v>6898946</v>
+        <v>6898988</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2048,10 +2047,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133623434</v>
+        <v>133623414</v>
       </c>
       <c r="B16" t="n">
-        <v>91967</v>
+        <v>91974</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2083,10 +2082,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620262</v>
+        <v>620154</v>
       </c>
       <c r="R16" t="n">
-        <v>6898976</v>
+        <v>6899021</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2145,10 +2144,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133623411</v>
+        <v>133623425</v>
       </c>
       <c r="B17" t="n">
-        <v>79398</v>
+        <v>91974</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2155,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2179,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620166</v>
+        <v>620196</v>
       </c>
       <c r="R17" t="n">
-        <v>6898962</v>
+        <v>6898959</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2242,54 +2241,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133623442</v>
+        <v>133623428</v>
       </c>
       <c r="B18" t="n">
-        <v>4776</v>
+        <v>91974</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100299</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620347</v>
+        <v>620196</v>
       </c>
       <c r="R18" t="n">
-        <v>6898852</v>
+        <v>6898931</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2330,7 +2320,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2349,10 +2338,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133623431</v>
+        <v>133623429</v>
       </c>
       <c r="B19" t="n">
-        <v>79366</v>
+        <v>91974</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2360,21 +2349,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2373,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620266</v>
+        <v>620275</v>
       </c>
       <c r="R19" t="n">
-        <v>6898928</v>
+        <v>6898905</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2446,10 +2435,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133623443</v>
+        <v>133623434</v>
       </c>
       <c r="B20" t="n">
-        <v>79366</v>
+        <v>91974</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2457,21 +2446,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620349</v>
+        <v>620262</v>
       </c>
       <c r="R20" t="n">
-        <v>6898850</v>
+        <v>6898976</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2543,10 +2532,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133623465</v>
+        <v>133623436</v>
       </c>
       <c r="B21" t="n">
-        <v>79985</v>
+        <v>91974</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2554,21 +2543,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2578,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620113</v>
+        <v>620349</v>
       </c>
       <c r="R21" t="n">
-        <v>6898932</v>
+        <v>6898946</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2640,10 +2629,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133623423</v>
+        <v>133623444</v>
       </c>
       <c r="B22" t="n">
-        <v>79366</v>
+        <v>91974</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,21 +2640,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2675,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620235</v>
+        <v>620341</v>
       </c>
       <c r="R22" t="n">
-        <v>6898952</v>
+        <v>6898817</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2737,10 +2726,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133623448</v>
+        <v>133623445</v>
       </c>
       <c r="B23" t="n">
-        <v>57975</v>
+        <v>91974</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,42 +2737,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620324</v>
+        <v>620349</v>
       </c>
       <c r="R23" t="n">
-        <v>6898861</v>
+        <v>6898830</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2813,11 +2797,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2844,32 +2823,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133623452</v>
+        <v>133623450</v>
       </c>
       <c r="B24" t="n">
-        <v>91930</v>
+        <v>91974</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2879,10 +2858,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620384</v>
+        <v>620351</v>
       </c>
       <c r="R24" t="n">
-        <v>6898898</v>
+        <v>6898926</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2941,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133623422</v>
+        <v>133623456</v>
       </c>
       <c r="B25" t="n">
-        <v>80481</v>
+        <v>91974</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2952,21 +2931,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2976,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620275</v>
+        <v>620264</v>
       </c>
       <c r="R25" t="n">
-        <v>6898953</v>
+        <v>6898924</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3038,10 +3017,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133623444</v>
+        <v>133623458</v>
       </c>
       <c r="B26" t="n">
-        <v>91967</v>
+        <v>91974</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3073,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620341</v>
+        <v>620239</v>
       </c>
       <c r="R26" t="n">
-        <v>6898817</v>
+        <v>6898916</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3135,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133623402</v>
+        <v>133623466</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>91995</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3146,45 +3125,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620109</v>
+        <v>620116</v>
       </c>
       <c r="R27" t="n">
-        <v>6898948</v>
+        <v>6898986</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3240,53 +3211,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133623446</v>
+        <v>133623415</v>
       </c>
       <c r="B28" t="n">
-        <v>57975</v>
+        <v>91937</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620339</v>
+        <v>620235</v>
       </c>
       <c r="R28" t="n">
-        <v>6898847</v>
+        <v>6898961</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3345,7 +3311,7 @@
         <v>133623426</v>
       </c>
       <c r="B29" t="n">
-        <v>91930</v>
+        <v>91937</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3439,48 +3405,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133623463</v>
+        <v>133623432</v>
       </c>
       <c r="B30" t="n">
-        <v>92709</v>
+        <v>91937</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>757</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620142</v>
+        <v>620266</v>
       </c>
       <c r="R30" t="n">
-        <v>6898946</v>
+        <v>6898927</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3515,18 +3478,12 @@
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar på grov tallåga. Röd KOH-reaktion</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3545,32 +3502,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133623458</v>
+        <v>133623452</v>
       </c>
       <c r="B31" t="n">
-        <v>91967</v>
+        <v>91937</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3580,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620239</v>
+        <v>620384</v>
       </c>
       <c r="R31" t="n">
-        <v>6898916</v>
+        <v>6898898</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3642,32 +3599,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133623462</v>
+        <v>133623455</v>
       </c>
       <c r="B32" t="n">
-        <v>92709</v>
+        <v>91937</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>757</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3677,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620130</v>
+        <v>620268</v>
       </c>
       <c r="R32" t="n">
-        <v>6898930</v>
+        <v>6898926</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3713,11 +3670,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar. Röd KOH-reaktion</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3744,32 +3696,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133623438</v>
+        <v>133623464</v>
       </c>
       <c r="B33" t="n">
-        <v>79032</v>
+        <v>91937</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3779,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620335</v>
+        <v>620127</v>
       </c>
       <c r="R33" t="n">
-        <v>6898933</v>
+        <v>6898927</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3841,32 +3793,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133623433</v>
+        <v>133623401</v>
       </c>
       <c r="B34" t="n">
-        <v>83343</v>
+        <v>79373</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3876,10 +3828,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>620290</v>
+        <v>620094</v>
       </c>
       <c r="R34" t="n">
-        <v>6898929</v>
+        <v>6898985</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3938,32 +3890,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133623459</v>
+        <v>133623403</v>
       </c>
       <c r="B35" t="n">
-        <v>81348</v>
+        <v>79373</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3973,10 +3925,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>620266</v>
+        <v>620099</v>
       </c>
       <c r="R35" t="n">
-        <v>6898988</v>
+        <v>6898937</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4035,32 +3987,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133623464</v>
+        <v>133623407</v>
       </c>
       <c r="B36" t="n">
-        <v>91930</v>
+        <v>79373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4070,10 +4022,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620127</v>
+        <v>620142</v>
       </c>
       <c r="R36" t="n">
-        <v>6898927</v>
+        <v>6898988</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4132,32 +4084,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133623421</v>
+        <v>133623413</v>
       </c>
       <c r="B37" t="n">
-        <v>79398</v>
+        <v>79373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4167,10 +4119,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620249</v>
+        <v>620178</v>
       </c>
       <c r="R37" t="n">
-        <v>6898992</v>
+        <v>6898953</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4229,32 +4181,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133623432</v>
+        <v>133623423</v>
       </c>
       <c r="B38" t="n">
-        <v>91930</v>
+        <v>79373</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4264,10 +4216,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>620266</v>
+        <v>620235</v>
       </c>
       <c r="R38" t="n">
-        <v>6898927</v>
+        <v>6898952</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4326,32 +4278,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133623437</v>
+        <v>133623431</v>
       </c>
       <c r="B39" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4361,10 +4313,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>620340</v>
+        <v>620266</v>
       </c>
       <c r="R39" t="n">
-        <v>6898950</v>
+        <v>6898928</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4423,53 +4375,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133623408</v>
+        <v>133623443</v>
       </c>
       <c r="B40" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långberget, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>620156</v>
+        <v>620349</v>
       </c>
       <c r="R40" t="n">
-        <v>6898981</v>
+        <v>6898850</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4525,32 +4472,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133623424</v>
+        <v>133623447</v>
       </c>
       <c r="B41" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4560,10 +4507,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>620238</v>
+        <v>620318</v>
       </c>
       <c r="R41" t="n">
-        <v>6898939</v>
+        <v>6898875</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4622,32 +4569,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133623428</v>
+        <v>133623453</v>
       </c>
       <c r="B42" t="n">
-        <v>91967</v>
+        <v>79373</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4657,10 +4604,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620196</v>
+        <v>620262</v>
       </c>
       <c r="R42" t="n">
-        <v>6898931</v>
+        <v>6898935</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4719,10 +4666,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133623404</v>
+        <v>133623400</v>
       </c>
       <c r="B43" t="n">
-        <v>79398</v>
+        <v>79130</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4730,21 +4677,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4754,10 +4701,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620098</v>
+        <v>620043</v>
       </c>
       <c r="R43" t="n">
-        <v>6898939</v>
+        <v>6898980</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4816,10 +4763,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133623439</v>
+        <v>133623424</v>
       </c>
       <c r="B44" t="n">
-        <v>79398</v>
+        <v>79992</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4827,21 +4774,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4851,10 +4798,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>620336</v>
+        <v>620238</v>
       </c>
       <c r="R44" t="n">
-        <v>6898875</v>
+        <v>6898939</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4913,10 +4860,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133623412</v>
+        <v>133623437</v>
       </c>
       <c r="B45" t="n">
-        <v>79398</v>
+        <v>79992</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4924,21 +4871,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4948,10 +4895,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>620162</v>
+        <v>620340</v>
       </c>
       <c r="R45" t="n">
-        <v>6899008</v>
+        <v>6898950</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5010,10 +4957,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133623445</v>
+        <v>133623465</v>
       </c>
       <c r="B46" t="n">
-        <v>91967</v>
+        <v>79992</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5021,21 +4968,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5045,10 +4992,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>620349</v>
+        <v>620113</v>
       </c>
       <c r="R46" t="n">
-        <v>6898830</v>
+        <v>6898932</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5110,7 +5057,7 @@
         <v>133623417</v>
       </c>
       <c r="B47" t="n">
-        <v>80481</v>
+        <v>80488</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5204,10 +5151,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133623425</v>
+        <v>133623420</v>
       </c>
       <c r="B48" t="n">
-        <v>91967</v>
+        <v>80488</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5215,21 +5162,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5239,10 +5186,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620196</v>
+        <v>620219</v>
       </c>
       <c r="R48" t="n">
-        <v>6898959</v>
+        <v>6899013</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5301,10 +5248,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133623453</v>
+        <v>133623422</v>
       </c>
       <c r="B49" t="n">
-        <v>79366</v>
+        <v>80488</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5312,21 +5259,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5336,10 +5283,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>620262</v>
+        <v>620275</v>
       </c>
       <c r="R49" t="n">
-        <v>6898935</v>
+        <v>6898953</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5398,32 +5345,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133623466</v>
+        <v>133623418</v>
       </c>
       <c r="B50" t="n">
-        <v>91988</v>
+        <v>80493</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5433,10 +5380,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>620116</v>
+        <v>620220</v>
       </c>
       <c r="R50" t="n">
-        <v>6898986</v>
+        <v>6899021</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5495,10 +5442,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133623456</v>
+        <v>133623469</v>
       </c>
       <c r="B51" t="n">
-        <v>91967</v>
+        <v>78377</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5506,21 +5453,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6487</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5530,10 +5477,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>620264</v>
+        <v>620116</v>
       </c>
       <c r="R51" t="n">
-        <v>6898924</v>
+        <v>6899013</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5592,10 +5539,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133815458</v>
+        <v>133623402</v>
       </c>
       <c r="B52" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5603,37 +5550,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -5643,13 +5582,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>620217</v>
+        <v>620109</v>
       </c>
       <c r="R52" t="n">
-        <v>6898924</v>
+        <v>6898948</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5702,6 +5641,1235 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>133623408</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Långberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>620156</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6898981</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>133623446</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Långberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>620339</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6898847</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>133623448</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Långberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>620324</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6898861</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>133623460</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Långberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>620244</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6898934</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>133623442</v>
+      </c>
+      <c r="B57" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Långberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>620347</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6898852</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>133623440</v>
+      </c>
+      <c r="B58" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Långberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>620348</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6898859</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>133815458</v>
+      </c>
+      <c r="B59" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Långberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>620217</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6898924</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>133623398</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Långberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>620052</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6898981</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>133623409</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Långberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>620161</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6898969</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>133623468</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Långberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>620112</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6899014</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>133623467</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Långberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>620113</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6899000</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>133623451</v>
+      </c>
+      <c r="B64" t="n">
+        <v>92322</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6331024</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Skeletocutis delicata</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Miettinen &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Långberget, Mpd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>620359</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6898922</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På gammal fruktkropp av ullticka, undersidan av en granlåga. Typisk doft av skeletocutis, tydligt slitsade porer.</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
